--- a/焊缝统计R3_auto(1).xlsx
+++ b/焊缝统计R3_auto(1).xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Sam\2026MIS\焊接机器人\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\hanf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2726A365-352C-410A-9915-FBB07D07C421}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C94A95A-3A27-4062-AC36-4783E21CACAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6420" yWindow="380" windowWidth="12980" windowHeight="13770" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="焊缝统计" sheetId="1" r:id="rId1"/>
     <sheet name="异常报告" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">焊缝统计!$A$1:$J$419</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">焊缝统计!$A$1:$I$419</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
 </workbook>
@@ -409,14 +409,14 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -721,18 +721,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:J419"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="14" style="5" customWidth="1"/>
-    <col min="3" max="3" width="23.875" style="5" customWidth="1"/>
+    <col min="3" max="3" width="23.90625" style="5" customWidth="1"/>
     <col min="4" max="8" width="14" style="5" customWidth="1"/>
-    <col min="9" max="9" width="23.75" style="5" customWidth="1"/>
-    <col min="10" max="10" width="12.5" style="5" customWidth="1"/>
+    <col min="9" max="9" width="23.7265625" style="5" customWidth="1"/>
+    <col min="10" max="10" width="12.453125" style="5" customWidth="1"/>
     <col min="11" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -762,7 +763,7 @@
       </c>
       <c r="J1" s="4"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
         <v>1</v>
       </c>
@@ -785,7 +786,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
         <v>2</v>
       </c>
@@ -808,7 +809,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
         <v>3</v>
       </c>
@@ -831,7 +832,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <v>4</v>
       </c>
@@ -854,7 +855,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <v>5</v>
       </c>
@@ -877,7 +878,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <v>6</v>
       </c>
@@ -900,7 +901,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
         <v>7</v>
       </c>
@@ -923,7 +924,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <v>8</v>
       </c>
@@ -946,7 +947,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
         <v>9</v>
       </c>
@@ -969,7 +970,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <v>10</v>
       </c>
@@ -992,7 +993,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
         <v>11</v>
       </c>
@@ -1015,7 +1016,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
         <v>12</v>
       </c>
@@ -1038,7 +1039,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
         <v>13</v>
       </c>
@@ -1061,7 +1062,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
         <v>14</v>
       </c>
@@ -1084,7 +1085,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5">
         <v>15</v>
       </c>
@@ -1107,7 +1108,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
         <v>16</v>
       </c>
@@ -1130,7 +1131,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5">
         <v>17</v>
       </c>
@@ -1153,7 +1154,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5">
         <v>18</v>
       </c>
@@ -1176,7 +1177,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5">
         <v>19</v>
       </c>
@@ -1199,7 +1200,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
         <v>20</v>
       </c>
@@ -1222,7 +1223,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5">
         <v>21</v>
       </c>
@@ -1245,7 +1246,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
         <v>22</v>
       </c>
@@ -1268,7 +1269,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5">
         <v>23</v>
       </c>
@@ -1291,7 +1292,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5">
         <v>24</v>
       </c>
@@ -1314,7 +1315,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="5">
         <v>25</v>
       </c>
@@ -1337,7 +1338,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5">
         <v>26</v>
       </c>
@@ -1360,7 +1361,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5">
         <v>27</v>
       </c>
@@ -1383,7 +1384,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5">
         <v>28</v>
       </c>
@@ -1406,7 +1407,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="5">
         <v>29</v>
       </c>
@@ -1429,7 +1430,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5">
         <v>30</v>
       </c>
@@ -1452,7 +1453,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="5">
         <v>31</v>
       </c>
@@ -1475,7 +1476,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="5">
         <v>32</v>
       </c>
@@ -1498,7 +1499,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="5">
         <v>33</v>
       </c>
@@ -1521,7 +1522,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="5">
         <v>34</v>
       </c>
@@ -1544,7 +1545,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="5">
         <v>35</v>
       </c>
@@ -1567,7 +1568,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="5">
         <v>36</v>
       </c>
@@ -1590,7 +1591,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="5">
         <v>37</v>
       </c>
@@ -1613,7 +1614,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="5">
         <v>38</v>
       </c>
@@ -1636,7 +1637,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="5">
         <v>39</v>
       </c>
@@ -1659,7 +1660,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="5">
         <v>40</v>
       </c>
@@ -1682,7 +1683,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="5">
         <v>41</v>
       </c>
@@ -1705,7 +1706,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="5">
         <v>42</v>
       </c>
@@ -1728,7 +1729,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="5">
         <v>43</v>
       </c>
@@ -1751,7 +1752,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="5">
         <v>44</v>
       </c>
@@ -1774,7 +1775,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="5">
         <v>45</v>
       </c>
@@ -1797,7 +1798,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="5">
         <v>46</v>
       </c>
@@ -1820,7 +1821,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="5">
         <v>47</v>
       </c>
@@ -1843,7 +1844,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="5">
         <v>48</v>
       </c>
@@ -1866,7 +1867,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="5">
         <v>49</v>
       </c>
@@ -1889,7 +1890,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="5">
         <v>50</v>
       </c>
@@ -1912,7 +1913,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" s="5">
         <v>51</v>
       </c>
@@ -1935,7 +1936,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" s="5">
         <v>52</v>
       </c>
@@ -1958,7 +1959,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="5">
         <v>53</v>
       </c>
@@ -1981,7 +1982,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="5">
         <v>54</v>
       </c>
@@ -2004,7 +2005,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" s="5">
         <v>55</v>
       </c>
@@ -2027,7 +2028,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" s="5">
         <v>56</v>
       </c>
@@ -2050,7 +2051,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" s="5">
         <v>57</v>
       </c>
@@ -2073,7 +2074,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" s="5">
         <v>58</v>
       </c>
@@ -2096,7 +2097,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="5">
         <v>59</v>
       </c>
@@ -2119,7 +2120,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" s="5">
         <v>60</v>
       </c>
@@ -2142,7 +2143,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="5">
         <v>61</v>
       </c>
@@ -2165,7 +2166,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" s="5">
         <v>62</v>
       </c>
@@ -2188,7 +2189,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" s="5">
         <v>63</v>
       </c>
@@ -2211,7 +2212,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" s="5">
         <v>64</v>
       </c>
@@ -2234,7 +2235,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" s="5">
         <v>65</v>
       </c>
@@ -2257,7 +2258,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" s="5">
         <v>66</v>
       </c>
@@ -2280,7 +2281,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" s="5">
         <v>67</v>
       </c>
@@ -2303,7 +2304,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" s="5">
         <v>68</v>
       </c>
@@ -2326,7 +2327,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" s="5">
         <v>69</v>
       </c>
@@ -2349,7 +2350,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" s="5">
         <v>70</v>
       </c>
@@ -2372,104 +2373,107 @@
         <v>18</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" s="5">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="B72" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C72" s="5">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D72" s="5">
-        <v>534</v>
+        <v>140</v>
       </c>
       <c r="F72" s="5" t="s">
         <v>20</v>
       </c>
       <c r="G72" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H72" s="5" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" s="5">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="B73" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C73" s="5">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D73" s="5">
-        <v>534</v>
+        <v>140</v>
       </c>
       <c r="F73" s="5" t="s">
         <v>20</v>
       </c>
       <c r="G73" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H73" s="5" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" s="5">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="B74" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C74" s="5">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D74" s="5">
-        <v>534</v>
+        <v>29</v>
       </c>
       <c r="F74" s="5" t="s">
         <v>20</v>
       </c>
       <c r="G74" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H74" s="5" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" s="5">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="B75" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C75" s="5">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D75" s="5">
-        <v>534</v>
+        <v>29</v>
       </c>
       <c r="F75" s="5" t="s">
         <v>20</v>
       </c>
       <c r="G75" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H75" s="5" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" s="5">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="B76" s="5" t="s">
         <v>8</v>
+      </c>
+      <c r="C76" s="5">
+        <v>7</v>
       </c>
       <c r="D76" s="5">
         <v>140</v>
@@ -2478,18 +2482,15 @@
         <v>20</v>
       </c>
       <c r="G76" s="5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H76" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="I76" s="5" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.15">
+    </row>
+    <row r="77" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" s="5">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="B77" s="5" t="s">
         <v>11</v>
@@ -2504,38 +2505,38 @@
         <v>20</v>
       </c>
       <c r="G77" s="5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H77" s="5" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" s="5">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="B78" s="5" t="s">
         <v>8</v>
       </c>
+      <c r="C78" s="5">
+        <v>7</v>
+      </c>
       <c r="D78" s="5">
-        <v>270</v>
+        <v>29</v>
       </c>
       <c r="F78" s="5" t="s">
         <v>20</v>
       </c>
       <c r="G78" s="5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H78" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="I78" s="5" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.15">
+    </row>
+    <row r="79" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" s="5">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="B79" s="5" t="s">
         <v>11</v>
@@ -2544,44 +2545,44 @@
         <v>7</v>
       </c>
       <c r="D79" s="5">
-        <v>270</v>
+        <v>29</v>
       </c>
       <c r="F79" s="5" t="s">
         <v>20</v>
       </c>
       <c r="G79" s="5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H79" s="5" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" s="5">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="B80" s="5" t="s">
         <v>8</v>
+      </c>
+      <c r="C80" s="5">
+        <v>7</v>
       </c>
       <c r="D80" s="5">
         <v>140</v>
       </c>
       <c r="F80" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G80" s="5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H80" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="I80" s="5" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.15">
+    </row>
+    <row r="81" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" s="5">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="B81" s="5" t="s">
         <v>11</v>
@@ -2593,179 +2594,179 @@
         <v>140</v>
       </c>
       <c r="F81" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G81" s="5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H81" s="5" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" s="5">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="B82" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C82" s="5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D82" s="5">
-        <v>200</v>
+        <v>140</v>
       </c>
       <c r="F82" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G82" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H82" s="5" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" s="5">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="B83" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C83" s="5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D83" s="5">
-        <v>200</v>
+        <v>140</v>
       </c>
       <c r="F83" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G83" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H83" s="5" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" s="5">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="B84" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C84" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D84" s="5">
-        <v>140</v>
+        <v>534</v>
       </c>
       <c r="F84" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G84" s="5" t="s">
         <v>21</v>
-      </c>
-      <c r="G84" s="5" t="s">
-        <v>24</v>
       </c>
       <c r="H84" s="5" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" s="5">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="B85" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C85" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D85" s="5">
-        <v>140</v>
+        <v>534</v>
       </c>
       <c r="F85" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G85" s="5" t="s">
         <v>21</v>
-      </c>
-      <c r="G85" s="5" t="s">
-        <v>24</v>
       </c>
       <c r="H85" s="5" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" s="5">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="B86" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C86" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D86" s="5">
-        <v>140</v>
+        <v>534</v>
       </c>
       <c r="F86" s="5" t="s">
         <v>20</v>
       </c>
       <c r="G86" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="H86" s="5" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" s="5">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="B87" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C87" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D87" s="5">
-        <v>140</v>
+        <v>534</v>
       </c>
       <c r="F87" s="5" t="s">
         <v>20</v>
       </c>
       <c r="G87" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="H87" s="5" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" s="5">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="B88" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C88" s="5">
-        <v>7</v>
-      </c>
       <c r="D88" s="5">
-        <v>29</v>
+        <v>140</v>
       </c>
       <c r="F88" s="5" t="s">
         <v>20</v>
       </c>
       <c r="G88" s="5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H88" s="5" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="I88" s="5" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" s="5">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="B89" s="5" t="s">
         <v>11</v>
@@ -2774,27 +2775,27 @@
         <v>7</v>
       </c>
       <c r="D89" s="5">
-        <v>29</v>
+        <v>140</v>
       </c>
       <c r="F89" s="5" t="s">
         <v>20</v>
       </c>
       <c r="G89" s="5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H89" s="5" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" s="5">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="B90" s="5" t="s">
         <v>8</v>
       </c>
       <c r="D90" s="5">
-        <v>140</v>
+        <v>270</v>
       </c>
       <c r="F90" s="5" t="s">
         <v>20</v>
@@ -2809,9 +2810,9 @@
         <v>85</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" s="5">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="B91" s="5" t="s">
         <v>11</v>
@@ -2820,7 +2821,7 @@
         <v>7</v>
       </c>
       <c r="D91" s="5">
-        <v>140</v>
+        <v>270</v>
       </c>
       <c r="F91" s="5" t="s">
         <v>20</v>
@@ -2832,15 +2833,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" s="5">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="B92" s="5" t="s">
         <v>8</v>
       </c>
       <c r="D92" s="5">
-        <v>270</v>
+        <v>140</v>
       </c>
       <c r="F92" s="5" t="s">
         <v>20</v>
@@ -2852,12 +2853,12 @@
         <v>20</v>
       </c>
       <c r="I92" s="5" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.15">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" s="5">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="B93" s="5" t="s">
         <v>11</v>
@@ -2866,7 +2867,7 @@
         <v>7</v>
       </c>
       <c r="D93" s="5">
-        <v>270</v>
+        <v>140</v>
       </c>
       <c r="F93" s="5" t="s">
         <v>20</v>
@@ -2878,9 +2879,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" s="5">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="B94" s="5" t="s">
         <v>8</v>
@@ -2901,9 +2902,9 @@
         <v>85</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" s="5">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="B95" s="5" t="s">
         <v>11</v>
@@ -2924,32 +2925,32 @@
         <v>20</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" s="5">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="B96" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C96" s="5">
-        <v>7</v>
-      </c>
       <c r="D96" s="5">
-        <v>140</v>
+        <v>270</v>
       </c>
       <c r="F96" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G96" s="5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H96" s="5" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="I96" s="5" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" s="5">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="B97" s="5" t="s">
         <v>11</v>
@@ -2958,27 +2959,24 @@
         <v>7</v>
       </c>
       <c r="D97" s="5">
-        <v>140</v>
+        <v>270</v>
       </c>
       <c r="F97" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G97" s="5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H97" s="5" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="98" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" s="5">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="B98" s="5" t="s">
         <v>8</v>
-      </c>
-      <c r="C98" s="5">
-        <v>7</v>
       </c>
       <c r="D98" s="5">
         <v>140</v>
@@ -2987,15 +2985,18 @@
         <v>20</v>
       </c>
       <c r="G98" s="5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H98" s="5" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="I98" s="5" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" s="5">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B99" s="5" t="s">
         <v>11</v>
@@ -3010,38 +3011,38 @@
         <v>20</v>
       </c>
       <c r="G99" s="5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H99" s="5" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" s="5">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="B100" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C100" s="5">
-        <v>7</v>
-      </c>
       <c r="D100" s="5">
-        <v>29</v>
+        <v>140</v>
       </c>
       <c r="F100" s="5" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G100" s="5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H100" s="5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="101" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+        <v>25</v>
+      </c>
+      <c r="I100" s="5" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="5">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="B101" s="5" t="s">
         <v>11</v>
@@ -3050,67 +3051,67 @@
         <v>7</v>
       </c>
       <c r="D101" s="5">
-        <v>29</v>
+        <v>140</v>
       </c>
       <c r="F101" s="5" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G101" s="5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H101" s="5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.15">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102" s="5">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B102" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C102" s="5">
-        <v>9</v>
-      </c>
       <c r="D102" s="5">
-        <v>440</v>
+        <v>268</v>
       </c>
       <c r="F102" s="5" t="s">
         <v>25</v>
       </c>
       <c r="G102" s="5" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="H102" s="5" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="I102" s="5" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103" s="5">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="B103" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C103" s="5">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D103" s="5">
-        <v>440</v>
+        <v>268</v>
       </c>
       <c r="F103" s="5" t="s">
         <v>25</v>
       </c>
       <c r="G103" s="5" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="H103" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104" s="5">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="B104" s="5" t="s">
         <v>8</v>
@@ -3131,9 +3132,9 @@
         <v>85</v>
       </c>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105" s="5">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="B105" s="5" t="s">
         <v>11</v>
@@ -3154,15 +3155,15 @@
         <v>25</v>
       </c>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106" s="5">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="B106" s="5" t="s">
         <v>8</v>
       </c>
       <c r="D106" s="5">
-        <v>268</v>
+        <v>140</v>
       </c>
       <c r="F106" s="5" t="s">
         <v>25</v>
@@ -3177,9 +3178,9 @@
         <v>85</v>
       </c>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A107" s="5">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="B107" s="5" t="s">
         <v>11</v>
@@ -3188,7 +3189,7 @@
         <v>7</v>
       </c>
       <c r="D107" s="5">
-        <v>268</v>
+        <v>140</v>
       </c>
       <c r="F107" s="5" t="s">
         <v>25</v>
@@ -3200,15 +3201,15 @@
         <v>25</v>
       </c>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108" s="5">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="B108" s="5" t="s">
         <v>8</v>
       </c>
       <c r="D108" s="5">
-        <v>140</v>
+        <v>268</v>
       </c>
       <c r="F108" s="5" t="s">
         <v>25</v>
@@ -3223,9 +3224,9 @@
         <v>85</v>
       </c>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109" s="5">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="B109" s="5" t="s">
         <v>11</v>
@@ -3234,7 +3235,7 @@
         <v>7</v>
       </c>
       <c r="D109" s="5">
-        <v>140</v>
+        <v>268</v>
       </c>
       <c r="F109" s="5" t="s">
         <v>25</v>
@@ -3246,15 +3247,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110" s="5">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="B110" s="5" t="s">
         <v>8</v>
-      </c>
-      <c r="C110" s="5">
-        <v>6</v>
       </c>
       <c r="D110" s="5">
         <v>140</v>
@@ -3263,21 +3261,24 @@
         <v>25</v>
       </c>
       <c r="G110" s="5" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="H110" s="5" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="I110" s="5" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111" s="5">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="B111" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C111" s="5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D111" s="5">
         <v>140</v>
@@ -3286,84 +3287,84 @@
         <v>25</v>
       </c>
       <c r="G111" s="5" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="H111" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="112" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" s="5">
-        <v>111</v>
+        <v>81</v>
       </c>
       <c r="B112" s="5" t="s">
         <v>8</v>
       </c>
+      <c r="C112" s="5">
+        <v>6</v>
+      </c>
       <c r="D112" s="5">
+        <v>200</v>
+      </c>
+      <c r="F112" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G112" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H112" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A113" s="5">
+        <v>82</v>
+      </c>
+      <c r="B113" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C113" s="5">
+        <v>6</v>
+      </c>
+      <c r="D113" s="5">
+        <v>200</v>
+      </c>
+      <c r="F113" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G113" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H113" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A114" s="5">
+        <v>119</v>
+      </c>
+      <c r="B114" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C114" s="5">
+        <v>7</v>
+      </c>
+      <c r="D114" s="5">
         <v>140</v>
-      </c>
-      <c r="F112" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="G112" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="H112" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="I112" s="5" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A113" s="5">
-        <v>112</v>
-      </c>
-      <c r="B113" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C113" s="5">
-        <v>7</v>
-      </c>
-      <c r="D113" s="5">
-        <v>140</v>
-      </c>
-      <c r="F113" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="G113" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="H113" s="5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A114" s="5">
-        <v>113</v>
-      </c>
-      <c r="B114" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D114" s="5">
-        <v>268</v>
       </c>
       <c r="F114" s="5" t="s">
         <v>25</v>
       </c>
       <c r="G114" s="5" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="H114" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="I114" s="5" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.15">
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115" s="5">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="B115" s="5" t="s">
         <v>11</v>
@@ -3372,44 +3373,44 @@
         <v>7</v>
       </c>
       <c r="D115" s="5">
-        <v>268</v>
+        <v>140</v>
       </c>
       <c r="F115" s="5" t="s">
         <v>25</v>
       </c>
       <c r="G115" s="5" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="H115" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116" s="5">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="B116" s="5" t="s">
         <v>8</v>
       </c>
+      <c r="C116" s="5">
+        <v>7</v>
+      </c>
       <c r="D116" s="5">
-        <v>140</v>
+        <v>33</v>
       </c>
       <c r="F116" s="5" t="s">
         <v>25</v>
       </c>
       <c r="G116" s="5" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="H116" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="I116" s="5" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.15">
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117" s="5">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="B117" s="5" t="s">
         <v>11</v>
@@ -3418,73 +3419,73 @@
         <v>7</v>
       </c>
       <c r="D117" s="5">
-        <v>140</v>
+        <v>33</v>
       </c>
       <c r="F117" s="5" t="s">
         <v>25</v>
       </c>
       <c r="G117" s="5" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="H117" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118" s="5">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="B118" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C118" s="5">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D118" s="5">
-        <v>140</v>
+        <v>440</v>
       </c>
       <c r="F118" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G118" s="5" t="s">
         <v>26</v>
-      </c>
-      <c r="G118" s="5" t="s">
-        <v>28</v>
       </c>
       <c r="H118" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119" s="5">
-        <v>118</v>
+        <v>102</v>
       </c>
       <c r="B119" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C119" s="5">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D119" s="5">
-        <v>140</v>
+        <v>440</v>
       </c>
       <c r="F119" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G119" s="5" t="s">
         <v>26</v>
-      </c>
-      <c r="G119" s="5" t="s">
-        <v>28</v>
       </c>
       <c r="H119" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A120" s="5">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="B120" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C120" s="5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D120" s="5">
         <v>140</v>
@@ -3493,21 +3494,21 @@
         <v>25</v>
       </c>
       <c r="G120" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H120" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121" s="5">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="B121" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C121" s="5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D121" s="5">
         <v>140</v>
@@ -3516,15 +3517,15 @@
         <v>25</v>
       </c>
       <c r="G121" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H121" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122" s="5">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B122" s="5" t="s">
         <v>8</v>
@@ -3533,10 +3534,10 @@
         <v>7</v>
       </c>
       <c r="D122" s="5">
-        <v>33</v>
+        <v>140</v>
       </c>
       <c r="F122" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G122" s="5" t="s">
         <v>28</v>
@@ -3545,9 +3546,9 @@
         <v>25</v>
       </c>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A123" s="5">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="B123" s="5" t="s">
         <v>11</v>
@@ -3556,10 +3557,10 @@
         <v>7</v>
       </c>
       <c r="D123" s="5">
-        <v>33</v>
+        <v>140</v>
       </c>
       <c r="F123" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G123" s="5" t="s">
         <v>28</v>
@@ -3568,7 +3569,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="124" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" s="5">
         <v>123</v>
       </c>
@@ -3591,7 +3592,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="125" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" s="5">
         <v>124</v>
       </c>
@@ -3614,7 +3615,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="126" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" s="5">
         <v>125</v>
       </c>
@@ -3637,7 +3638,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="127" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" s="5">
         <v>126</v>
       </c>
@@ -3660,7 +3661,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="128" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" s="5">
         <v>127</v>
       </c>
@@ -3683,7 +3684,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="129" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" s="5">
         <v>128</v>
       </c>
@@ -3706,7 +3707,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="130" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" s="5">
         <v>129</v>
       </c>
@@ -3729,7 +3730,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="131" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" s="5">
         <v>130</v>
       </c>
@@ -3752,7 +3753,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="132" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" s="5">
         <v>131</v>
       </c>
@@ -3775,7 +3776,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="133" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" s="5">
         <v>132</v>
       </c>
@@ -3798,7 +3799,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="134" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" s="5">
         <v>133</v>
       </c>
@@ -3821,7 +3822,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="135" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" s="5">
         <v>134</v>
       </c>
@@ -3844,1111 +3845,1111 @@
         <v>61</v>
       </c>
     </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="136" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" s="5">
+        <v>145</v>
+      </c>
+      <c r="B136" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C136" s="5">
+        <v>7</v>
+      </c>
+      <c r="D136" s="5">
+        <v>313</v>
+      </c>
+      <c r="F136" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G136" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="H136" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A137" s="5">
+        <v>146</v>
+      </c>
+      <c r="B137" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C137" s="5">
+        <v>7</v>
+      </c>
+      <c r="D137" s="5">
+        <v>313</v>
+      </c>
+      <c r="F137" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G137" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="H137" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A138" s="5">
+        <v>141</v>
+      </c>
+      <c r="B138" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C138" s="5">
+        <v>7</v>
+      </c>
+      <c r="D138" s="5">
+        <v>90.5</v>
+      </c>
+      <c r="F138" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="G138" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="H138" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A139" s="5">
+        <v>142</v>
+      </c>
+      <c r="B139" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C139" s="5">
+        <v>7</v>
+      </c>
+      <c r="D139" s="5">
+        <v>90.5</v>
+      </c>
+      <c r="F139" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="G139" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="H139" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A140" s="5">
+        <v>143</v>
+      </c>
+      <c r="B140" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C140" s="5">
+        <v>7</v>
+      </c>
+      <c r="D140" s="5">
+        <v>90.5</v>
+      </c>
+      <c r="F140" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="G140" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="H140" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A141" s="5">
+        <v>144</v>
+      </c>
+      <c r="B141" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C141" s="5">
+        <v>7</v>
+      </c>
+      <c r="D141" s="5">
+        <v>90.5</v>
+      </c>
+      <c r="F141" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="G141" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="H141" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A142" s="5">
         <v>135</v>
       </c>
-      <c r="B136" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C136" s="5">
-        <v>7</v>
-      </c>
-      <c r="D136" s="5">
+      <c r="B142" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C142" s="5">
+        <v>7</v>
+      </c>
+      <c r="D142" s="5">
         <v>115</v>
       </c>
-      <c r="F136" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="G136" s="5" t="s">
+      <c r="F142" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G142" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="H136" s="5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A137" s="5">
+      <c r="H142" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A143" s="5">
         <v>136</v>
       </c>
-      <c r="B137" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C137" s="5">
-        <v>7</v>
-      </c>
-      <c r="D137" s="5">
+      <c r="B143" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C143" s="5">
+        <v>7</v>
+      </c>
+      <c r="D143" s="5">
         <v>115</v>
       </c>
-      <c r="F137" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="G137" s="5" t="s">
+      <c r="F143" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G143" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="H137" s="5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A138" s="5">
+      <c r="H143" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A144" s="5">
         <v>137</v>
       </c>
-      <c r="B138" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C138" s="5">
-        <v>7</v>
-      </c>
-      <c r="D138" s="5">
+      <c r="B144" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C144" s="5">
+        <v>7</v>
+      </c>
+      <c r="D144" s="5">
         <v>220</v>
       </c>
-      <c r="F138" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="G138" s="5" t="s">
+      <c r="F144" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G144" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="H138" s="5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A139" s="5">
+      <c r="H144" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="145" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A145" s="5">
         <v>138</v>
       </c>
-      <c r="B139" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C139" s="5">
-        <v>7</v>
-      </c>
-      <c r="D139" s="5">
+      <c r="B145" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C145" s="5">
+        <v>7</v>
+      </c>
+      <c r="D145" s="5">
         <v>220</v>
       </c>
-      <c r="F139" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="G139" s="5" t="s">
+      <c r="F145" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G145" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="H139" s="5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A140" s="5">
+      <c r="H145" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="146" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A146" s="5">
         <v>139</v>
       </c>
-      <c r="B140" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C140" s="5">
-        <v>7</v>
-      </c>
-      <c r="D140" s="5">
+      <c r="B146" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C146" s="5">
+        <v>7</v>
+      </c>
+      <c r="D146" s="5">
         <v>115</v>
       </c>
-      <c r="F140" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="G140" s="5" t="s">
+      <c r="F146" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G146" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="H140" s="5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A141" s="5">
+      <c r="H146" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="147" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A147" s="5">
         <v>140</v>
       </c>
-      <c r="B141" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C141" s="5">
-        <v>7</v>
-      </c>
-      <c r="D141" s="5">
+      <c r="B147" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C147" s="5">
+        <v>7</v>
+      </c>
+      <c r="D147" s="5">
         <v>115</v>
       </c>
-      <c r="F141" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="G141" s="5" t="s">
+      <c r="F147" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G147" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="H141" s="5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A142" s="5">
-        <v>141</v>
-      </c>
-      <c r="B142" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C142" s="5">
-        <v>7</v>
-      </c>
-      <c r="D142" s="5">
+      <c r="H147" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="148" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A148" s="5">
+        <v>171</v>
+      </c>
+      <c r="B148" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D148" s="5">
+        <v>116</v>
+      </c>
+      <c r="F148" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G148" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="H148" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="I148" s="5" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="149" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A149" s="5">
+        <v>172</v>
+      </c>
+      <c r="B149" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C149" s="5">
+        <v>9</v>
+      </c>
+      <c r="D149" s="5">
+        <v>116</v>
+      </c>
+      <c r="F149" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G149" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="H149" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="150" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A150" s="5">
+        <v>173</v>
+      </c>
+      <c r="B150" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D150" s="5">
+        <v>220</v>
+      </c>
+      <c r="F150" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G150" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="H150" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="I150" s="5" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="151" spans="1:9" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A151" s="5">
+        <v>174</v>
+      </c>
+      <c r="B151" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C151" s="5">
+        <v>7</v>
+      </c>
+      <c r="D151" s="5">
+        <v>220</v>
+      </c>
+      <c r="F151" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G151" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="H151" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="152" spans="1:9" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A152" s="5">
+        <v>175</v>
+      </c>
+      <c r="B152" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D152" s="5">
+        <v>116</v>
+      </c>
+      <c r="F152" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G152" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="H152" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="I152" s="5" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="153" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A153" s="5">
+        <v>176</v>
+      </c>
+      <c r="B153" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C153" s="5">
+        <v>9</v>
+      </c>
+      <c r="D153" s="5">
+        <v>116</v>
+      </c>
+      <c r="F153" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G153" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="H153" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="154" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A154" s="5">
+        <v>177</v>
+      </c>
+      <c r="B154" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D154" s="5">
+        <v>116</v>
+      </c>
+      <c r="F154" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G154" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="H154" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="I154" s="5" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="155" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A155" s="5">
+        <v>178</v>
+      </c>
+      <c r="B155" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C155" s="5">
+        <v>9</v>
+      </c>
+      <c r="D155" s="5">
+        <v>116</v>
+      </c>
+      <c r="F155" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G155" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="H155" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="156" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A156" s="5">
+        <v>179</v>
+      </c>
+      <c r="B156" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D156" s="5">
+        <v>220</v>
+      </c>
+      <c r="F156" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G156" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="H156" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="I156" s="5" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="157" spans="1:9" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A157" s="5">
+        <v>180</v>
+      </c>
+      <c r="B157" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C157" s="5">
+        <v>7</v>
+      </c>
+      <c r="D157" s="5">
+        <v>220</v>
+      </c>
+      <c r="F157" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G157" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="H157" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="158" spans="1:9" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A158" s="5">
+        <v>181</v>
+      </c>
+      <c r="B158" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D158" s="5">
+        <v>116</v>
+      </c>
+      <c r="F158" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G158" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="H158" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="I158" s="5" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="159" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A159" s="5">
+        <v>182</v>
+      </c>
+      <c r="B159" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C159" s="5">
+        <v>9</v>
+      </c>
+      <c r="D159" s="5">
+        <v>116</v>
+      </c>
+      <c r="F159" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G159" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="H159" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="160" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A160" s="5">
+        <v>165</v>
+      </c>
+      <c r="B160" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C160" s="5">
+        <v>9</v>
+      </c>
+      <c r="D160" s="5">
+        <v>115</v>
+      </c>
+      <c r="F160" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G160" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="H160" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="161" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A161" s="5">
+        <v>166</v>
+      </c>
+      <c r="B161" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C161" s="5">
+        <v>9</v>
+      </c>
+      <c r="D161" s="5">
+        <v>115</v>
+      </c>
+      <c r="F161" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G161" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="H161" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="162" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A162" s="5">
+        <v>167</v>
+      </c>
+      <c r="B162" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C162" s="5">
+        <v>7</v>
+      </c>
+      <c r="D162" s="5">
+        <v>220</v>
+      </c>
+      <c r="F162" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G162" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="H162" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="163" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A163" s="5">
+        <v>168</v>
+      </c>
+      <c r="B163" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C163" s="5">
+        <v>7</v>
+      </c>
+      <c r="D163" s="5">
+        <v>220</v>
+      </c>
+      <c r="F163" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G163" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="H163" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="164" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A164" s="5">
+        <v>169</v>
+      </c>
+      <c r="B164" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C164" s="5">
+        <v>9</v>
+      </c>
+      <c r="D164" s="5">
+        <v>115</v>
+      </c>
+      <c r="F164" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G164" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="H164" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="165" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A165" s="5">
+        <v>170</v>
+      </c>
+      <c r="B165" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C165" s="5">
+        <v>9</v>
+      </c>
+      <c r="D165" s="5">
+        <v>115</v>
+      </c>
+      <c r="F165" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G165" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="H165" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="166" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A166" s="5">
+        <v>147</v>
+      </c>
+      <c r="B166" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C166" s="5">
+        <v>7</v>
+      </c>
+      <c r="D166" s="5">
         <v>90.5</v>
       </c>
-      <c r="F142" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="G142" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="H142" s="5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A143" s="5">
-        <v>142</v>
-      </c>
-      <c r="B143" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C143" s="5">
-        <v>7</v>
-      </c>
-      <c r="D143" s="5">
+      <c r="F166" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G166" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="H166" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="167" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A167" s="5">
+        <v>148</v>
+      </c>
+      <c r="B167" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C167" s="5">
+        <v>7</v>
+      </c>
+      <c r="D167" s="5">
         <v>90.5</v>
       </c>
-      <c r="F143" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="G143" s="5" t="s">
+      <c r="F167" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G167" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="H167" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="168" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A168" s="5">
+        <v>149</v>
+      </c>
+      <c r="B168" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C168" s="5">
+        <v>7</v>
+      </c>
+      <c r="D168" s="5">
+        <v>60</v>
+      </c>
+      <c r="F168" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G168" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="H168" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="169" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A169" s="5">
+        <v>150</v>
+      </c>
+      <c r="B169" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C169" s="5">
+        <v>7</v>
+      </c>
+      <c r="D169" s="5">
+        <v>60</v>
+      </c>
+      <c r="F169" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G169" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="H169" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="170" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A170" s="5">
+        <v>151</v>
+      </c>
+      <c r="B170" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C170" s="5">
+        <v>7</v>
+      </c>
+      <c r="D170" s="5">
+        <v>90.5</v>
+      </c>
+      <c r="F170" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="H143" s="5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A144" s="5">
-        <v>143</v>
-      </c>
-      <c r="B144" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C144" s="5">
-        <v>7</v>
-      </c>
-      <c r="D144" s="5">
+      <c r="G170" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="H170" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="171" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A171" s="5">
+        <v>152</v>
+      </c>
+      <c r="B171" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C171" s="5">
+        <v>7</v>
+      </c>
+      <c r="D171" s="5">
         <v>90.5</v>
       </c>
-      <c r="F144" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="G144" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="H144" s="5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A145" s="5">
-        <v>144</v>
-      </c>
-      <c r="B145" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C145" s="5">
-        <v>7</v>
-      </c>
-      <c r="D145" s="5">
+      <c r="F171" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="G171" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="H171" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="172" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A172" s="5">
+        <v>153</v>
+      </c>
+      <c r="B172" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C172" s="5">
+        <v>7</v>
+      </c>
+      <c r="D172" s="5">
         <v>90.5</v>
       </c>
-      <c r="F145" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="G145" s="5" t="s">
+      <c r="F172" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G172" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="H172" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="173" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A173" s="5">
+        <v>154</v>
+      </c>
+      <c r="B173" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C173" s="5">
+        <v>7</v>
+      </c>
+      <c r="D173" s="5">
+        <v>90.5</v>
+      </c>
+      <c r="F173" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G173" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="H173" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="174" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A174" s="5">
+        <v>155</v>
+      </c>
+      <c r="B174" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C174" s="5">
+        <v>7</v>
+      </c>
+      <c r="D174" s="5">
+        <v>60</v>
+      </c>
+      <c r="F174" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G174" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="H174" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="175" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A175" s="5">
+        <v>156</v>
+      </c>
+      <c r="B175" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C175" s="5">
+        <v>7</v>
+      </c>
+      <c r="D175" s="5">
+        <v>60</v>
+      </c>
+      <c r="F175" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G175" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="H175" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="176" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A176" s="5">
+        <v>157</v>
+      </c>
+      <c r="B176" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C176" s="5">
+        <v>7</v>
+      </c>
+      <c r="D176" s="5">
+        <v>90.5</v>
+      </c>
+      <c r="F176" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="H145" s="5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A146" s="5">
-        <v>145</v>
-      </c>
-      <c r="B146" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C146" s="5">
-        <v>7</v>
-      </c>
-      <c r="D146" s="5">
-        <v>313</v>
-      </c>
-      <c r="F146" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="G146" s="5" t="s">
+      <c r="G176" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="H176" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="177" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A177" s="5">
+        <v>158</v>
+      </c>
+      <c r="B177" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C177" s="5">
+        <v>7</v>
+      </c>
+      <c r="D177" s="5">
+        <v>90.5</v>
+      </c>
+      <c r="F177" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="H146" s="5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A147" s="5">
-        <v>146</v>
-      </c>
-      <c r="B147" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C147" s="5">
-        <v>7</v>
-      </c>
-      <c r="D147" s="5">
-        <v>313</v>
-      </c>
-      <c r="F147" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="G147" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="H147" s="5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A148" s="5">
-        <v>147</v>
-      </c>
-      <c r="B148" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C148" s="5">
-        <v>7</v>
-      </c>
-      <c r="D148" s="5">
-        <v>90.5</v>
-      </c>
-      <c r="F148" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="G148" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="H148" s="5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A149" s="5">
-        <v>148</v>
-      </c>
-      <c r="B149" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C149" s="5">
-        <v>7</v>
-      </c>
-      <c r="D149" s="5">
-        <v>90.5</v>
-      </c>
-      <c r="F149" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="G149" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="H149" s="5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A150" s="5">
-        <v>149</v>
-      </c>
-      <c r="B150" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C150" s="5">
-        <v>7</v>
-      </c>
-      <c r="D150" s="5">
-        <v>60</v>
-      </c>
-      <c r="F150" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="G150" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="H150" s="5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="151" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A151" s="5">
-        <v>150</v>
-      </c>
-      <c r="B151" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C151" s="5">
-        <v>7</v>
-      </c>
-      <c r="D151" s="5">
-        <v>60</v>
-      </c>
-      <c r="F151" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="G151" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="H151" s="5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="152" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A152" s="5">
-        <v>151</v>
-      </c>
-      <c r="B152" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C152" s="5">
-        <v>7</v>
-      </c>
-      <c r="D152" s="5">
-        <v>90.5</v>
-      </c>
-      <c r="F152" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="G152" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="H152" s="5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="153" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A153" s="5">
-        <v>152</v>
-      </c>
-      <c r="B153" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C153" s="5">
-        <v>7</v>
-      </c>
-      <c r="D153" s="5">
-        <v>90.5</v>
-      </c>
-      <c r="F153" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="G153" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="H153" s="5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="154" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A154" s="5">
-        <v>153</v>
-      </c>
-      <c r="B154" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C154" s="5">
-        <v>7</v>
-      </c>
-      <c r="D154" s="5">
-        <v>90.5</v>
-      </c>
-      <c r="F154" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="G154" s="5" t="s">
+      <c r="G177" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="H154" s="5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="155" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A155" s="5">
-        <v>154</v>
-      </c>
-      <c r="B155" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C155" s="5">
-        <v>7</v>
-      </c>
-      <c r="D155" s="5">
-        <v>90.5</v>
-      </c>
-      <c r="F155" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="G155" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="H155" s="5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A156" s="5">
-        <v>155</v>
-      </c>
-      <c r="B156" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C156" s="5">
-        <v>7</v>
-      </c>
-      <c r="D156" s="5">
-        <v>60</v>
-      </c>
-      <c r="F156" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="G156" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="H156" s="5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="157" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A157" s="5">
-        <v>156</v>
-      </c>
-      <c r="B157" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C157" s="5">
-        <v>7</v>
-      </c>
-      <c r="D157" s="5">
-        <v>60</v>
-      </c>
-      <c r="F157" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="G157" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="H157" s="5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="158" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A158" s="5">
-        <v>157</v>
-      </c>
-      <c r="B158" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C158" s="5">
-        <v>7</v>
-      </c>
-      <c r="D158" s="5">
-        <v>90.5</v>
-      </c>
-      <c r="F158" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="G158" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="H158" s="5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="159" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A159" s="5">
-        <v>158</v>
-      </c>
-      <c r="B159" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C159" s="5">
-        <v>7</v>
-      </c>
-      <c r="D159" s="5">
-        <v>90.5</v>
-      </c>
-      <c r="F159" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="G159" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="H159" s="5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="160" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A160" s="5">
+      <c r="H177" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="178" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A178" s="5">
         <v>159</v>
       </c>
-      <c r="B160" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C160" s="5">
-        <v>7</v>
-      </c>
-      <c r="D160" s="5">
+      <c r="B178" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C178" s="5">
+        <v>7</v>
+      </c>
+      <c r="D178" s="5">
         <v>250</v>
       </c>
-      <c r="F160" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="G160" s="5" t="s">
+      <c r="F178" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G178" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="H160" s="5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A161" s="5">
+      <c r="H178" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="179" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A179" s="5">
         <v>160</v>
       </c>
-      <c r="B161" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C161" s="5">
-        <v>7</v>
-      </c>
-      <c r="D161" s="5">
+      <c r="B179" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C179" s="5">
+        <v>7</v>
+      </c>
+      <c r="D179" s="5">
         <v>250</v>
       </c>
-      <c r="F161" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="G161" s="5" t="s">
+      <c r="F179" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G179" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="H161" s="5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A162" s="5">
+      <c r="H179" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="180" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A180" s="5">
         <v>161</v>
       </c>
-      <c r="B162" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C162" s="5">
-        <v>7</v>
-      </c>
-      <c r="D162" s="5">
+      <c r="B180" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C180" s="5">
+        <v>7</v>
+      </c>
+      <c r="D180" s="5">
         <v>172</v>
       </c>
-      <c r="F162" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="G162" s="5" t="s">
+      <c r="F180" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G180" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="H162" s="5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A163" s="5">
+      <c r="H180" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="181" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A181" s="5">
         <v>162</v>
       </c>
-      <c r="B163" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C163" s="5">
-        <v>7</v>
-      </c>
-      <c r="D163" s="5">
+      <c r="B181" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C181" s="5">
+        <v>7</v>
+      </c>
+      <c r="D181" s="5">
         <v>172</v>
       </c>
-      <c r="F163" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="G163" s="5" t="s">
+      <c r="F181" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G181" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="H163" s="5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A164" s="5">
+      <c r="H181" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="182" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A182" s="5">
         <v>163</v>
       </c>
-      <c r="B164" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C164" s="5">
-        <v>7</v>
-      </c>
-      <c r="D164" s="5">
+      <c r="B182" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C182" s="5">
+        <v>7</v>
+      </c>
+      <c r="D182" s="5">
         <v>250</v>
       </c>
-      <c r="F164" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="G164" s="5" t="s">
+      <c r="F182" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G182" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="H164" s="5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A165" s="5">
+      <c r="H182" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="183" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A183" s="5">
         <v>164</v>
       </c>
-      <c r="B165" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C165" s="5">
-        <v>7</v>
-      </c>
-      <c r="D165" s="5">
+      <c r="B183" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C183" s="5">
+        <v>7</v>
+      </c>
+      <c r="D183" s="5">
         <v>250</v>
       </c>
-      <c r="F165" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="G165" s="5" t="s">
+      <c r="F183" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G183" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="H165" s="5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A166" s="5">
-        <v>165</v>
-      </c>
-      <c r="B166" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C166" s="5">
-        <v>9</v>
-      </c>
-      <c r="D166" s="5">
-        <v>115</v>
-      </c>
-      <c r="F166" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="G166" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="H166" s="5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A167" s="5">
-        <v>166</v>
-      </c>
-      <c r="B167" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C167" s="5">
-        <v>9</v>
-      </c>
-      <c r="D167" s="5">
-        <v>115</v>
-      </c>
-      <c r="F167" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="G167" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="H167" s="5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A168" s="5">
-        <v>167</v>
-      </c>
-      <c r="B168" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C168" s="5">
-        <v>7</v>
-      </c>
-      <c r="D168" s="5">
-        <v>220</v>
-      </c>
-      <c r="F168" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="G168" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="H168" s="5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A169" s="5">
-        <v>168</v>
-      </c>
-      <c r="B169" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C169" s="5">
-        <v>7</v>
-      </c>
-      <c r="D169" s="5">
-        <v>220</v>
-      </c>
-      <c r="F169" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="G169" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="H169" s="5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A170" s="5">
-        <v>169</v>
-      </c>
-      <c r="B170" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C170" s="5">
-        <v>9</v>
-      </c>
-      <c r="D170" s="5">
-        <v>115</v>
-      </c>
-      <c r="F170" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="G170" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="H170" s="5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A171" s="5">
-        <v>170</v>
-      </c>
-      <c r="B171" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C171" s="5">
-        <v>9</v>
-      </c>
-      <c r="D171" s="5">
-        <v>115</v>
-      </c>
-      <c r="F171" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="G171" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="H171" s="5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A172" s="5">
-        <v>171</v>
-      </c>
-      <c r="B172" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D172" s="5">
-        <v>116</v>
-      </c>
-      <c r="F172" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="G172" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="H172" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="I172" s="5" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A173" s="5">
-        <v>172</v>
-      </c>
-      <c r="B173" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C173" s="5">
-        <v>9</v>
-      </c>
-      <c r="D173" s="5">
-        <v>116</v>
-      </c>
-      <c r="F173" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="G173" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="H173" s="5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A174" s="5">
-        <v>173</v>
-      </c>
-      <c r="B174" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D174" s="5">
-        <v>220</v>
-      </c>
-      <c r="F174" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="G174" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="H174" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="I174" s="5" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A175" s="5">
-        <v>174</v>
-      </c>
-      <c r="B175" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C175" s="5">
-        <v>7</v>
-      </c>
-      <c r="D175" s="5">
-        <v>220</v>
-      </c>
-      <c r="F175" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="G175" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="H175" s="5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A176" s="5">
-        <v>175</v>
-      </c>
-      <c r="B176" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D176" s="5">
-        <v>116</v>
-      </c>
-      <c r="F176" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="G176" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="H176" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="I176" s="5" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A177" s="5">
-        <v>176</v>
-      </c>
-      <c r="B177" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C177" s="5">
-        <v>9</v>
-      </c>
-      <c r="D177" s="5">
-        <v>116</v>
-      </c>
-      <c r="F177" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="G177" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="H177" s="5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A178" s="5">
-        <v>177</v>
-      </c>
-      <c r="B178" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D178" s="5">
-        <v>116</v>
-      </c>
-      <c r="F178" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="G178" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="H178" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="I178" s="5" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A179" s="5">
-        <v>178</v>
-      </c>
-      <c r="B179" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C179" s="5">
-        <v>9</v>
-      </c>
-      <c r="D179" s="5">
-        <v>116</v>
-      </c>
-      <c r="F179" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="G179" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="H179" s="5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A180" s="5">
-        <v>179</v>
-      </c>
-      <c r="B180" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D180" s="5">
-        <v>220</v>
-      </c>
-      <c r="F180" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="G180" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="H180" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="I180" s="5" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A181" s="5">
-        <v>180</v>
-      </c>
-      <c r="B181" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C181" s="5">
-        <v>7</v>
-      </c>
-      <c r="D181" s="5">
-        <v>220</v>
-      </c>
-      <c r="F181" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="G181" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="H181" s="5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A182" s="5">
-        <v>181</v>
-      </c>
-      <c r="B182" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D182" s="5">
-        <v>116</v>
-      </c>
-      <c r="F182" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="G182" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="H182" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="I182" s="5" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A183" s="5">
-        <v>182</v>
-      </c>
-      <c r="B183" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C183" s="5">
-        <v>9</v>
-      </c>
-      <c r="D183" s="5">
-        <v>116</v>
-      </c>
-      <c r="F183" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="G183" s="5" t="s">
-        <v>31</v>
-      </c>
       <c r="H183" s="5" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="184" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A184" s="5">
         <v>183</v>
       </c>
@@ -4971,7 +4972,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="185" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A185" s="5">
         <v>184</v>
       </c>
@@ -4994,7 +4995,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="186" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A186" s="5">
         <v>185</v>
       </c>
@@ -5017,7 +5018,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="187" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A187" s="5">
         <v>186</v>
       </c>
@@ -5040,7 +5041,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="188" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A188" s="5">
         <v>187</v>
       </c>
@@ -5063,7 +5064,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="189" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A189" s="5">
         <v>188</v>
       </c>
@@ -5086,7 +5087,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="190" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="190" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A190" s="5">
         <v>189</v>
       </c>
@@ -5109,7 +5110,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="191" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="191" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A191" s="5">
         <v>190</v>
       </c>
@@ -5132,7 +5133,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="192" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="192" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A192" s="5">
         <v>191</v>
       </c>
@@ -5155,7 +5156,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="193" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="193" spans="1:8" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="5">
         <v>192</v>
       </c>
@@ -5178,7 +5179,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="194" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="194" spans="1:8" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="5">
         <v>193</v>
       </c>
@@ -5201,7 +5202,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="195" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="195" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A195" s="5">
         <v>194</v>
       </c>
@@ -5224,7 +5225,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="196" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="196" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A196" s="5">
         <v>195</v>
       </c>
@@ -5247,7 +5248,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="197" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="197" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A197" s="5">
         <v>196</v>
       </c>
@@ -5270,7 +5271,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="198" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="198" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A198" s="5">
         <v>197</v>
       </c>
@@ -5293,7 +5294,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="199" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="199" spans="1:8" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="5">
         <v>198</v>
       </c>
@@ -5316,7 +5317,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="200" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="200" spans="1:8" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="5">
         <v>199</v>
       </c>
@@ -5339,7 +5340,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="201" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="201" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A201" s="5">
         <v>200</v>
       </c>
@@ -5362,7 +5363,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="202" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="202" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A202" s="5">
         <v>201</v>
       </c>
@@ -5385,7 +5386,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="203" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="203" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A203" s="5">
         <v>202</v>
       </c>
@@ -5408,7 +5409,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="204" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="204" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A204" s="5">
         <v>203</v>
       </c>
@@ -5431,7 +5432,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="205" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="205" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A205" s="5">
         <v>204</v>
       </c>
@@ -5454,7 +5455,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="206" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="206" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A206" s="5">
         <v>205</v>
       </c>
@@ -5477,7 +5478,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="207" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="207" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A207" s="5">
         <v>206</v>
       </c>
@@ -5500,7 +5501,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="208" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="208" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A208" s="5">
         <v>207</v>
       </c>
@@ -5523,7 +5524,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="209" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="209" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A209" s="5">
         <v>208</v>
       </c>
@@ -5546,7 +5547,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="210" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="210" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A210" s="5">
         <v>209</v>
       </c>
@@ -5569,7 +5570,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="211" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="211" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A211" s="5">
         <v>210</v>
       </c>
@@ -5592,7 +5593,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="212" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="212" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A212" s="5">
         <v>211</v>
       </c>
@@ -5615,7 +5616,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="213" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="213" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A213" s="5">
         <v>212</v>
       </c>
@@ -5638,7 +5639,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="214" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="214" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A214" s="5">
         <v>213</v>
       </c>
@@ -5661,7 +5662,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="215" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="215" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A215" s="5">
         <v>214</v>
       </c>
@@ -5684,7 +5685,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="216" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="216" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A216" s="5">
         <v>215</v>
       </c>
@@ -5707,7 +5708,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="217" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="217" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A217" s="5">
         <v>216</v>
       </c>
@@ -5730,7 +5731,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="218" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="218" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A218" s="5">
         <v>217</v>
       </c>
@@ -5753,7 +5754,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="219" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="219" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A219" s="5">
         <v>218</v>
       </c>
@@ -5776,7 +5777,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="220" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="220" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A220" s="5">
         <v>219</v>
       </c>
@@ -5799,7 +5800,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="221" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="221" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A221" s="5">
         <v>220</v>
       </c>
@@ -5822,7 +5823,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="222" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="222" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A222" s="5">
         <v>221</v>
       </c>
@@ -5845,7 +5846,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="223" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="223" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A223" s="5">
         <v>222</v>
       </c>
@@ -5868,7 +5869,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="224" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="224" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A224" s="5">
         <v>223</v>
       </c>
@@ -5891,7 +5892,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="225" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="225" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A225" s="5">
         <v>224</v>
       </c>
@@ -5914,7 +5915,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="226" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="226" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A226" s="5">
         <v>225</v>
       </c>
@@ -5937,7 +5938,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="227" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="227" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A227" s="5">
         <v>226</v>
       </c>
@@ -5960,7 +5961,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="228" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="228" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A228" s="5">
         <v>227</v>
       </c>
@@ -5983,7 +5984,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="229" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="229" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A229" s="5">
         <v>228</v>
       </c>
@@ -6006,7 +6007,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="230" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="230" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A230" s="5">
         <v>229</v>
       </c>
@@ -6029,7 +6030,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="231" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="231" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A231" s="5">
         <v>230</v>
       </c>
@@ -6052,7 +6053,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="232" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="232" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A232" s="5">
         <v>231</v>
       </c>
@@ -6075,7 +6076,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="233" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="233" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A233" s="5">
         <v>232</v>
       </c>
@@ -6098,7 +6099,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="234" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="234" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A234" s="5">
         <v>233</v>
       </c>
@@ -6121,7 +6122,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="235" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="235" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A235" s="5">
         <v>234</v>
       </c>
@@ -6144,7 +6145,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="236" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="236" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A236" s="5">
         <v>235</v>
       </c>
@@ -6167,7 +6168,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="237" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="237" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A237" s="5">
         <v>236</v>
       </c>
@@ -6190,7 +6191,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="238" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="238" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A238" s="5">
         <v>237</v>
       </c>
@@ -6213,7 +6214,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="239" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="239" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A239" s="5">
         <v>238</v>
       </c>
@@ -6236,7 +6237,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="240" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="240" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A240" s="5">
         <v>239</v>
       </c>
@@ -6259,7 +6260,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="241" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="241" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A241" s="5">
         <v>240</v>
       </c>
@@ -6282,7 +6283,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="242" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="242" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A242" s="5">
         <v>241</v>
       </c>
@@ -6305,7 +6306,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="243" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="243" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A243" s="5">
         <v>242</v>
       </c>
@@ -6328,7 +6329,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="244" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="244" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A244" s="5">
         <v>243</v>
       </c>
@@ -6351,7 +6352,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="245" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="245" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A245" s="5">
         <v>244</v>
       </c>
@@ -6374,7 +6375,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="246" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="246" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A246" s="5">
         <v>245</v>
       </c>
@@ -6397,7 +6398,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="247" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="247" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A247" s="5">
         <v>246</v>
       </c>
@@ -6420,7 +6421,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="248" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="248" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A248" s="5">
         <v>247</v>
       </c>
@@ -6443,7 +6444,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="249" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="249" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A249" s="5">
         <v>248</v>
       </c>
@@ -6466,7 +6467,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="250" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="250" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A250" s="5">
         <v>249</v>
       </c>
@@ -6489,7 +6490,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="251" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="251" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A251" s="5">
         <v>250</v>
       </c>
@@ -6512,7 +6513,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="252" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="252" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A252" s="5">
         <v>251</v>
       </c>
@@ -6535,7 +6536,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="253" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="253" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A253" s="5">
         <v>252</v>
       </c>
@@ -6558,7 +6559,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="254" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="254" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A254" s="5">
         <v>253</v>
       </c>
@@ -6581,7 +6582,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="255" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="255" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A255" s="5">
         <v>254</v>
       </c>
@@ -6604,7 +6605,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="256" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="256" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A256" s="5">
         <v>255</v>
       </c>
@@ -6627,7 +6628,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="257" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="257" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A257" s="5">
         <v>256</v>
       </c>
@@ -6650,7 +6651,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="258" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="258" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A258" s="5">
         <v>257</v>
       </c>
@@ -6673,7 +6674,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="259" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="259" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A259" s="5">
         <v>258</v>
       </c>
@@ -6696,7 +6697,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="260" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="260" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A260" s="5">
         <v>259</v>
       </c>
@@ -6719,7 +6720,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="261" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="261" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A261" s="5">
         <v>260</v>
       </c>
@@ -6742,7 +6743,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="262" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="262" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A262" s="5">
         <v>261</v>
       </c>
@@ -6765,7 +6766,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="263" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="263" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A263" s="5">
         <v>262</v>
       </c>
@@ -6788,7 +6789,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="264" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="264" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A264" s="5">
         <v>263</v>
       </c>
@@ -6811,7 +6812,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="265" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="265" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A265" s="5">
         <v>264</v>
       </c>
@@ -6834,7 +6835,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="266" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="266" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A266" s="5">
         <v>265</v>
       </c>
@@ -6857,7 +6858,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="267" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="267" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A267" s="5">
         <v>266</v>
       </c>
@@ -6880,7 +6881,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="268" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="268" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A268" s="5">
         <v>267</v>
       </c>
@@ -6903,7 +6904,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="269" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="269" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A269" s="5">
         <v>268</v>
       </c>
@@ -6926,7 +6927,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="270" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="270" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A270" s="5">
         <v>269</v>
       </c>
@@ -6949,7 +6950,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="271" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="271" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A271" s="5">
         <v>270</v>
       </c>
@@ -6972,7 +6973,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="272" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="272" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A272" s="5">
         <v>271</v>
       </c>
@@ -6995,7 +6996,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="273" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="273" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A273" s="5">
         <v>272</v>
       </c>
@@ -7018,7 +7019,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="274" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="274" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A274" s="5">
         <v>273</v>
       </c>
@@ -7041,7 +7042,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="275" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="275" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A275" s="5">
         <v>274</v>
       </c>
@@ -7064,7 +7065,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="276" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="276" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A276" s="5">
         <v>275</v>
       </c>
@@ -7087,7 +7088,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="277" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="277" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A277" s="5">
         <v>276</v>
       </c>
@@ -7110,7 +7111,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="278" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="278" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A278" s="5">
         <v>277</v>
       </c>
@@ -7133,7 +7134,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="279" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="279" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A279" s="5">
         <v>278</v>
       </c>
@@ -7156,7 +7157,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="280" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="280" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A280" s="5">
         <v>279</v>
       </c>
@@ -7179,7 +7180,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="281" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="281" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A281" s="5">
         <v>280</v>
       </c>
@@ -7202,7 +7203,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="282" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="282" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A282" s="5">
         <v>281</v>
       </c>
@@ -7225,7 +7226,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="283" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="283" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A283" s="5">
         <v>282</v>
       </c>
@@ -7248,7 +7249,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="284" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="284" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A284" s="5">
         <v>283</v>
       </c>
@@ -7271,7 +7272,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="285" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="285" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A285" s="5">
         <v>284</v>
       </c>
@@ -7294,7 +7295,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="286" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="286" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A286" s="5">
         <v>285</v>
       </c>
@@ -7317,7 +7318,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="287" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="287" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A287" s="5">
         <v>286</v>
       </c>
@@ -7340,7 +7341,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="288" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="288" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A288" s="5">
         <v>287</v>
       </c>
@@ -7363,7 +7364,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="289" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="289" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A289" s="5">
         <v>288</v>
       </c>
@@ -7386,7 +7387,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="290" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="290" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A290" s="5">
         <v>289</v>
       </c>
@@ -7409,7 +7410,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="291" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="291" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A291" s="5">
         <v>290</v>
       </c>
@@ -7432,7 +7433,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="292" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="292" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A292" s="5">
         <v>291</v>
       </c>
@@ -7455,7 +7456,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="293" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="293" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A293" s="5">
         <v>292</v>
       </c>
@@ -7478,7 +7479,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="294" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="294" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A294" s="5">
         <v>293</v>
       </c>
@@ -7501,7 +7502,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="295" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="295" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A295" s="5">
         <v>294</v>
       </c>
@@ -7524,7 +7525,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="296" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="296" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A296" s="5">
         <v>295</v>
       </c>
@@ -7547,7 +7548,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="297" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="297" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A297" s="5">
         <v>296</v>
       </c>
@@ -7570,7 +7571,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="298" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="298" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A298" s="5">
         <v>297</v>
       </c>
@@ -7593,7 +7594,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="299" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="299" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A299" s="5">
         <v>298</v>
       </c>
@@ -7616,7 +7617,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="300" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="300" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A300" s="5">
         <v>299</v>
       </c>
@@ -7639,7 +7640,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="301" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="301" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A301" s="5">
         <v>300</v>
       </c>
@@ -7662,7 +7663,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="302" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="302" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A302" s="5">
         <v>301</v>
       </c>
@@ -7685,7 +7686,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="303" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="303" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A303" s="5">
         <v>302</v>
       </c>
@@ -7708,7 +7709,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="304" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="304" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A304" s="5">
         <v>303</v>
       </c>
@@ -7731,7 +7732,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="305" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="305" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A305" s="5">
         <v>304</v>
       </c>
@@ -7754,7 +7755,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="306" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="306" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A306" s="5">
         <v>305</v>
       </c>
@@ -7777,7 +7778,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="307" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="307" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A307" s="5">
         <v>306</v>
       </c>
@@ -7800,7 +7801,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="308" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="308" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A308" s="5">
         <v>307</v>
       </c>
@@ -7823,7 +7824,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="309" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="309" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A309" s="5">
         <v>308</v>
       </c>
@@ -7846,7 +7847,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="310" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="310" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A310" s="5">
         <v>309</v>
       </c>
@@ -7869,7 +7870,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="311" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="311" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A311" s="5">
         <v>310</v>
       </c>
@@ -7892,7 +7893,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="312" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="312" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A312" s="5">
         <v>311</v>
       </c>
@@ -7915,7 +7916,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="313" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="313" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A313" s="5">
         <v>312</v>
       </c>
@@ -7938,7 +7939,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="314" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="314" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A314" s="5">
         <v>313</v>
       </c>
@@ -7961,7 +7962,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="315" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="315" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A315" s="5">
         <v>314</v>
       </c>
@@ -7984,7 +7985,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="316" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="316" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A316" s="5">
         <v>315</v>
       </c>
@@ -8007,7 +8008,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="317" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="317" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A317" s="5">
         <v>316</v>
       </c>
@@ -8030,7 +8031,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="318" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="318" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A318" s="5">
         <v>317</v>
       </c>
@@ -8053,7 +8054,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="319" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="319" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A319" s="5">
         <v>318</v>
       </c>
@@ -8076,7 +8077,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="320" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="320" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A320" s="5">
         <v>319</v>
       </c>
@@ -8099,7 +8100,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="321" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="321" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A321" s="5">
         <v>320</v>
       </c>
@@ -8122,7 +8123,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="322" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="322" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A322" s="5">
         <v>321</v>
       </c>
@@ -8145,7 +8146,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="323" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="323" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A323" s="5">
         <v>322</v>
       </c>
@@ -8168,7 +8169,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="324" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="324" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A324" s="5">
         <v>323</v>
       </c>
@@ -8191,7 +8192,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="325" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="325" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A325" s="5">
         <v>324</v>
       </c>
@@ -8214,7 +8215,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="326" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="326" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A326" s="5">
         <v>325</v>
       </c>
@@ -8237,7 +8238,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="327" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="327" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A327" s="5">
         <v>326</v>
       </c>
@@ -8260,7 +8261,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="328" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="328" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A328" s="5">
         <v>327</v>
       </c>
@@ -8283,7 +8284,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="329" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="329" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A329" s="5">
         <v>328</v>
       </c>
@@ -8306,7 +8307,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="330" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="330" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A330" s="5">
         <v>329</v>
       </c>
@@ -8329,7 +8330,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="331" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="331" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A331" s="5">
         <v>330</v>
       </c>
@@ -8352,7 +8353,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="332" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="332" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A332" s="5">
         <v>331</v>
       </c>
@@ -8375,7 +8376,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="333" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="333" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A333" s="5">
         <v>332</v>
       </c>
@@ -8398,7 +8399,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="334" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="334" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A334" s="5">
         <v>333</v>
       </c>
@@ -8421,7 +8422,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="335" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="335" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A335" s="5">
         <v>334</v>
       </c>
@@ -8444,7 +8445,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="336" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="336" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A336" s="5">
         <v>335</v>
       </c>
@@ -8467,7 +8468,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="337" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="337" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A337" s="5">
         <v>336</v>
       </c>
@@ -8490,7 +8491,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="338" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="338" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A338" s="5">
         <v>337</v>
       </c>
@@ -8513,7 +8514,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="339" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="339" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A339" s="5">
         <v>338</v>
       </c>
@@ -8536,7 +8537,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="340" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="340" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A340" s="5">
         <v>339</v>
       </c>
@@ -8559,7 +8560,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="341" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="341" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A341" s="5">
         <v>340</v>
       </c>
@@ -8582,7 +8583,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="342" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="342" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A342" s="5">
         <v>341</v>
       </c>
@@ -8605,7 +8606,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="343" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="343" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A343" s="5">
         <v>342</v>
       </c>
@@ -8628,7 +8629,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="344" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="344" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A344" s="5">
         <v>343</v>
       </c>
@@ -8651,7 +8652,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="345" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="345" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A345" s="5">
         <v>344</v>
       </c>
@@ -8674,7 +8675,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="346" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="346" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A346" s="5">
         <v>345</v>
       </c>
@@ -8697,7 +8698,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="347" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="347" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A347" s="5">
         <v>346</v>
       </c>
@@ -8720,7 +8721,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="348" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="348" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A348" s="5">
         <v>347</v>
       </c>
@@ -8743,7 +8744,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="349" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="349" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A349" s="5">
         <v>348</v>
       </c>
@@ -8766,7 +8767,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="350" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="350" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A350" s="5">
         <v>349</v>
       </c>
@@ -8789,7 +8790,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="351" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="351" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A351" s="5">
         <v>350</v>
       </c>
@@ -8812,7 +8813,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="352" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="352" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A352" s="5">
         <v>351</v>
       </c>
@@ -8835,7 +8836,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="353" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="353" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A353" s="5">
         <v>352</v>
       </c>
@@ -8858,7 +8859,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="354" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="354" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A354" s="5">
         <v>353</v>
       </c>
@@ -8881,7 +8882,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="355" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="355" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A355" s="5">
         <v>354</v>
       </c>
@@ -8904,7 +8905,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="356" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="356" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A356" s="5">
         <v>355</v>
       </c>
@@ -8927,7 +8928,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="357" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="357" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A357" s="5">
         <v>356</v>
       </c>
@@ -8950,7 +8951,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="358" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="358" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A358" s="5">
         <v>357</v>
       </c>
@@ -8973,7 +8974,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="359" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="359" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A359" s="5">
         <v>358</v>
       </c>
@@ -8996,7 +8997,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="360" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="360" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A360" s="5">
         <v>359</v>
       </c>
@@ -9019,7 +9020,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="361" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="361" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A361" s="5">
         <v>360</v>
       </c>
@@ -9042,7 +9043,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="362" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="362" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A362" s="5">
         <v>361</v>
       </c>
@@ -9065,7 +9066,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="363" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="363" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A363" s="5">
         <v>362</v>
       </c>
@@ -9088,7 +9089,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="364" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="364" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A364" s="5">
         <v>363</v>
       </c>
@@ -9111,7 +9112,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="365" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="365" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A365" s="5">
         <v>364</v>
       </c>
@@ -9134,7 +9135,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="366" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="366" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A366" s="5">
         <v>365</v>
       </c>
@@ -9157,7 +9158,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="367" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="367" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A367" s="5">
         <v>366</v>
       </c>
@@ -9180,7 +9181,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="368" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="368" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A368" s="5">
         <v>367</v>
       </c>
@@ -9203,7 +9204,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="369" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="369" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A369" s="5">
         <v>368</v>
       </c>
@@ -9226,7 +9227,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="370" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="370" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A370" s="5">
         <v>369</v>
       </c>
@@ -9249,7 +9250,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="371" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="371" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A371" s="5">
         <v>370</v>
       </c>
@@ -9272,7 +9273,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="372" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="372" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A372" s="5">
         <v>371</v>
       </c>
@@ -9295,7 +9296,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="373" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="373" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A373" s="5">
         <v>372</v>
       </c>
@@ -9318,7 +9319,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="374" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="374" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A374" s="5">
         <v>373</v>
       </c>
@@ -9341,7 +9342,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="375" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="375" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A375" s="5">
         <v>374</v>
       </c>
@@ -9364,7 +9365,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="376" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="376" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A376" s="5">
         <v>375</v>
       </c>
@@ -9387,7 +9388,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="377" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="377" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A377" s="5">
         <v>376</v>
       </c>
@@ -9410,7 +9411,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="378" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="378" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A378" s="5">
         <v>377</v>
       </c>
@@ -9433,7 +9434,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="379" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="379" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A379" s="5">
         <v>378</v>
       </c>
@@ -9456,7 +9457,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="380" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="380" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A380" s="5">
         <v>379</v>
       </c>
@@ -9479,7 +9480,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="381" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="381" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A381" s="5">
         <v>380</v>
       </c>
@@ -9502,7 +9503,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="382" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="382" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A382" s="5">
         <v>381</v>
       </c>
@@ -9525,7 +9526,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="383" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="383" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A383" s="5">
         <v>382</v>
       </c>
@@ -9548,7 +9549,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="384" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="384" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A384" s="5">
         <v>383</v>
       </c>
@@ -9571,7 +9572,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="385" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="385" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A385" s="5">
         <v>384</v>
       </c>
@@ -9594,7 +9595,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="386" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="386" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A386" s="5">
         <v>385</v>
       </c>
@@ -9617,7 +9618,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="387" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="387" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A387" s="5">
         <v>386</v>
       </c>
@@ -9640,7 +9641,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="388" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="388" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A388" s="5">
         <v>387</v>
       </c>
@@ -9663,7 +9664,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="389" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="389" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A389" s="5">
         <v>388</v>
       </c>
@@ -9686,7 +9687,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="390" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="390" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A390" s="5">
         <v>389</v>
       </c>
@@ -9709,7 +9710,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="391" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="391" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A391" s="5">
         <v>390</v>
       </c>
@@ -9732,7 +9733,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="392" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="392" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A392" s="5">
         <v>391</v>
       </c>
@@ -9755,7 +9756,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="393" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="393" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A393" s="5">
         <v>392</v>
       </c>
@@ -9778,7 +9779,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="394" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="394" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A394" s="5">
         <v>393</v>
       </c>
@@ -9801,7 +9802,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="395" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="395" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A395" s="5">
         <v>394</v>
       </c>
@@ -9824,7 +9825,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="396" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="396" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A396" s="5">
         <v>395</v>
       </c>
@@ -9847,7 +9848,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="397" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="397" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A397" s="5">
         <v>396</v>
       </c>
@@ -9870,7 +9871,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="398" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="398" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A398" s="5">
         <v>397</v>
       </c>
@@ -9893,7 +9894,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="399" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="399" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A399" s="5">
         <v>398</v>
       </c>
@@ -9916,7 +9917,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="400" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="400" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A400" s="5">
         <v>399</v>
       </c>
@@ -9939,7 +9940,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="401" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="401" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A401" s="5">
         <v>400</v>
       </c>
@@ -9962,7 +9963,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="402" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="402" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A402" s="5">
         <v>401</v>
       </c>
@@ -9985,7 +9986,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="403" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="403" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A403" s="5">
         <v>402</v>
       </c>
@@ -10008,7 +10009,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="404" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="404" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A404" s="5">
         <v>403</v>
       </c>
@@ -10031,7 +10032,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="405" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="405" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A405" s="5">
         <v>404</v>
       </c>
@@ -10054,7 +10055,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="406" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="406" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A406" s="5">
         <v>405</v>
       </c>
@@ -10077,7 +10078,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="407" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="407" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A407" s="5">
         <v>406</v>
       </c>
@@ -10100,7 +10101,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="408" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="408" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A408" s="5">
         <v>407</v>
       </c>
@@ -10123,7 +10124,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="409" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="409" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A409" s="5">
         <v>408</v>
       </c>
@@ -10146,7 +10147,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="410" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="410" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A410" s="5">
         <v>409</v>
       </c>
@@ -10169,7 +10170,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="411" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="411" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A411" s="5">
         <v>410</v>
       </c>
@@ -10192,7 +10193,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="412" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="412" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A412" s="5">
         <v>411</v>
       </c>
@@ -10215,7 +10216,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="413" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="413" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A413" s="5">
         <v>412</v>
       </c>
@@ -10238,7 +10239,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="414" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="414" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A414" s="5">
         <v>413</v>
       </c>
@@ -10261,7 +10262,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="415" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="415" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A415" s="5">
         <v>414</v>
       </c>
@@ -10284,7 +10285,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="416" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="416" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A416" s="5">
         <v>415</v>
       </c>
@@ -10307,7 +10308,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="417" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="417" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A417" s="5">
         <v>416</v>
       </c>
@@ -10330,7 +10331,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="418" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="418" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A418" s="5">
         <v>417</v>
       </c>
@@ -10353,7 +10354,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="419" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="419" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A419" s="5">
         <v>418</v>
       </c>
@@ -10377,7 +10378,16 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J419" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:I419" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="7">
+      <filters>
+        <filter val="BE023"/>
+      </filters>
+    </filterColumn>
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A136:I183">
+      <sortCondition ref="G1:G419"/>
+    </sortState>
+  </autoFilter>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -10387,15 +10397,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:K201"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="1"/>
     <col min="2" max="2" width="40" customWidth="1"/>
-    <col min="5" max="5" width="16.875" customWidth="1"/>
-    <col min="11" max="11" width="23.375" customWidth="1"/>
+    <col min="5" max="5" width="16.90625" customWidth="1"/>
+    <col min="11" max="11" width="23.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>46</v>
       </c>
@@ -10427,7 +10437,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D2">
         <v>1</v>
       </c>
@@ -10450,7 +10460,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D3">
         <v>2</v>
       </c>
@@ -10473,7 +10483,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D4">
         <v>3</v>
       </c>
@@ -10496,7 +10506,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D5">
         <v>4</v>
       </c>
@@ -10519,7 +10529,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D6">
         <v>5</v>
       </c>
@@ -10542,7 +10552,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D7">
         <v>6</v>
       </c>
@@ -10565,7 +10575,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D8">
         <v>7</v>
       </c>
@@ -10588,7 +10598,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D9">
         <v>8</v>
       </c>
@@ -10611,7 +10621,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D10">
         <v>9</v>
       </c>
@@ -10634,7 +10644,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D11">
         <v>10</v>
       </c>
@@ -10657,7 +10667,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D12">
         <v>11</v>
       </c>
@@ -10680,7 +10690,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D13">
         <v>12</v>
       </c>
@@ -10703,7 +10713,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D14">
         <v>13</v>
       </c>
@@ -10726,7 +10736,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D15">
         <v>14</v>
       </c>
@@ -10749,7 +10759,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D16">
         <v>15</v>
       </c>
@@ -10772,7 +10782,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="17" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D17">
         <v>16</v>
       </c>
@@ -10795,7 +10805,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="18" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D18">
         <v>17</v>
       </c>
@@ -10818,7 +10828,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="19" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D19">
         <v>18</v>
       </c>
@@ -10841,7 +10851,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="20" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D20">
         <v>19</v>
       </c>
@@ -10864,7 +10874,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="21" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="21" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D21">
         <v>20</v>
       </c>
@@ -10887,7 +10897,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="22" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="22" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D22">
         <v>21</v>
       </c>
@@ -10910,7 +10920,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="23" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="23" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D23">
         <v>22</v>
       </c>
@@ -10933,7 +10943,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="24" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="24" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D24">
         <v>23</v>
       </c>
@@ -10956,7 +10966,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="25" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="25" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D25">
         <v>24</v>
       </c>
@@ -10979,7 +10989,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="26" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="26" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D26">
         <v>25</v>
       </c>
@@ -11002,7 +11012,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="27" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="27" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D27">
         <v>26</v>
       </c>
@@ -11025,7 +11035,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="28" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="28" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D28">
         <v>27</v>
       </c>
@@ -11048,7 +11058,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="29" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="29" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D29">
         <v>28</v>
       </c>
@@ -11071,7 +11081,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="30" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="30" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D30">
         <v>29</v>
       </c>
@@ -11094,7 +11104,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="31" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="31" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D31">
         <v>30</v>
       </c>
@@ -11117,7 +11127,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="32" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="32" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D32">
         <v>31</v>
       </c>
@@ -11140,7 +11150,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="33" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="33" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D33">
         <v>32</v>
       </c>
@@ -11163,7 +11173,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="34" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="34" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D34">
         <v>33</v>
       </c>
@@ -11186,7 +11196,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="35" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="35" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D35">
         <v>34</v>
       </c>
@@ -11209,7 +11219,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="36" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="36" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D36">
         <v>35</v>
       </c>
@@ -11232,7 +11242,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="37" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="37" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D37">
         <v>36</v>
       </c>
@@ -11255,7 +11265,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="38" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="38" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D38">
         <v>37</v>
       </c>
@@ -11278,7 +11288,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="39" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="39" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D39">
         <v>38</v>
       </c>
@@ -11301,7 +11311,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="40" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="40" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D40">
         <v>39</v>
       </c>
@@ -11324,7 +11334,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="41" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="41" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D41">
         <v>40</v>
       </c>
@@ -11347,7 +11357,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="42" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="42" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D42">
         <v>41</v>
       </c>
@@ -11370,7 +11380,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="43" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="43" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D43">
         <v>42</v>
       </c>
@@ -11393,7 +11403,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="44" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="44" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D44">
         <v>43</v>
       </c>
@@ -11416,7 +11426,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="45" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="45" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D45">
         <v>44</v>
       </c>
@@ -11439,7 +11449,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="46" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="46" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D46">
         <v>45</v>
       </c>
@@ -11462,7 +11472,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="47" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="47" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D47">
         <v>46</v>
       </c>
@@ -11485,7 +11495,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="48" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="48" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D48">
         <v>47</v>
       </c>
@@ -11508,7 +11518,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="49" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="49" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D49">
         <v>48</v>
       </c>
@@ -11531,7 +11541,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="50" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="50" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D50">
         <v>49</v>
       </c>
@@ -11554,7 +11564,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="51" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="51" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D51">
         <v>50</v>
       </c>
@@ -11577,7 +11587,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="52" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="52" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D52">
         <v>51</v>
       </c>
@@ -11600,7 +11610,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="53" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="53" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D53">
         <v>52</v>
       </c>
@@ -11623,7 +11633,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="54" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="54" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D54">
         <v>53</v>
       </c>
@@ -11646,7 +11656,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="55" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="55" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D55">
         <v>54</v>
       </c>
@@ -11669,7 +11679,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="56" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="56" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D56">
         <v>55</v>
       </c>
@@ -11692,7 +11702,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="57" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="57" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D57">
         <v>56</v>
       </c>
@@ -11715,7 +11725,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="58" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="58" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D58">
         <v>57</v>
       </c>
@@ -11738,7 +11748,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="59" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="59" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D59">
         <v>58</v>
       </c>
@@ -11761,7 +11771,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="60" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="60" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D60">
         <v>59</v>
       </c>
@@ -11784,7 +11794,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="61" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="61" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D61">
         <v>60</v>
       </c>
@@ -11807,7 +11817,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="62" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="62" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D62">
         <v>61</v>
       </c>
@@ -11830,7 +11840,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="63" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="63" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D63">
         <v>62</v>
       </c>
@@ -11853,7 +11863,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="64" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="64" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D64">
         <v>63</v>
       </c>
@@ -11876,7 +11886,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="65" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="65" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D65">
         <v>64</v>
       </c>
@@ -11899,7 +11909,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="66" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="66" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D66">
         <v>65</v>
       </c>
@@ -11922,7 +11932,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="67" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="67" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D67">
         <v>66</v>
       </c>
@@ -11945,7 +11955,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="68" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="68" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D68">
         <v>67</v>
       </c>
@@ -11968,7 +11978,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="69" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="69" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D69">
         <v>68</v>
       </c>
@@ -11991,7 +12001,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="70" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="70" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D70">
         <v>69</v>
       </c>
@@ -12014,7 +12024,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="71" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="71" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D71">
         <v>70</v>
       </c>
@@ -12037,7 +12047,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="72" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="72" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D72">
         <v>71</v>
       </c>
@@ -12060,7 +12070,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="73" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="73" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D73">
         <v>72</v>
       </c>
@@ -12083,7 +12093,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="74" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="74" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D74">
         <v>73</v>
       </c>
@@ -12106,7 +12116,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="75" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="75" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D75">
         <v>74</v>
       </c>
@@ -12129,7 +12139,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="76" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="76" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D76">
         <v>75</v>
       </c>
@@ -12152,7 +12162,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="77" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="77" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D77">
         <v>76</v>
       </c>
@@ -12175,7 +12185,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="78" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="78" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D78">
         <v>77</v>
       </c>
@@ -12198,7 +12208,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="79" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="79" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D79">
         <v>78</v>
       </c>
@@ -12221,7 +12231,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="80" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="80" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D80">
         <v>79</v>
       </c>
@@ -12244,7 +12254,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="81" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="81" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D81">
         <v>80</v>
       </c>
@@ -12267,7 +12277,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="82" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="82" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D82">
         <v>81</v>
       </c>
@@ -12290,7 +12300,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="83" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="83" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D83">
         <v>82</v>
       </c>
@@ -12313,7 +12323,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="84" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="84" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D84">
         <v>83</v>
       </c>
@@ -12336,7 +12346,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="85" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="85" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D85">
         <v>84</v>
       </c>
@@ -12359,7 +12369,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="86" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="86" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D86">
         <v>85</v>
       </c>
@@ -12382,7 +12392,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="87" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="87" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D87">
         <v>86</v>
       </c>
@@ -12405,7 +12415,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="88" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="88" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D88">
         <v>87</v>
       </c>
@@ -12428,7 +12438,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="89" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="89" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D89">
         <v>88</v>
       </c>
@@ -12451,7 +12461,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="90" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="90" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D90">
         <v>89</v>
       </c>
@@ -12474,7 +12484,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="91" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="91" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D91">
         <v>90</v>
       </c>
@@ -12497,7 +12507,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="92" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="92" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D92">
         <v>91</v>
       </c>
@@ -12520,7 +12530,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="93" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="93" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D93">
         <v>92</v>
       </c>
@@ -12543,7 +12553,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="94" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="94" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D94">
         <v>93</v>
       </c>
@@ -12566,7 +12576,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="95" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="95" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D95">
         <v>94</v>
       </c>
@@ -12589,7 +12599,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="96" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="96" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D96">
         <v>95</v>
       </c>
@@ -12612,7 +12622,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="97" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="97" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D97">
         <v>96</v>
       </c>
@@ -12635,7 +12645,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="98" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="98" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D98">
         <v>97</v>
       </c>
@@ -12658,7 +12668,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="99" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="99" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D99">
         <v>98</v>
       </c>
@@ -12681,7 +12691,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="100" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="100" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D100">
         <v>99</v>
       </c>
@@ -12704,7 +12714,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="101" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="101" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D101">
         <v>100</v>
       </c>
@@ -12727,7 +12737,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="102" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="102" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D102">
         <v>101</v>
       </c>
@@ -12750,7 +12760,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="103" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="103" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D103">
         <v>102</v>
       </c>
@@ -12773,7 +12783,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="104" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="104" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D104">
         <v>103</v>
       </c>
@@ -12796,7 +12806,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="105" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="105" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D105">
         <v>104</v>
       </c>
@@ -12819,7 +12829,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="106" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="106" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D106">
         <v>105</v>
       </c>
@@ -12842,7 +12852,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="107" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="107" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D107">
         <v>106</v>
       </c>
@@ -12865,7 +12875,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="108" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="108" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D108">
         <v>107</v>
       </c>
@@ -12888,7 +12898,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="109" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="109" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D109">
         <v>108</v>
       </c>
@@ -12911,7 +12921,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="110" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="110" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D110">
         <v>109</v>
       </c>
@@ -12934,7 +12944,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="111" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="111" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D111">
         <v>110</v>
       </c>
@@ -12957,7 +12967,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="112" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="112" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D112">
         <v>111</v>
       </c>
@@ -12980,7 +12990,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="113" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="113" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D113">
         <v>112</v>
       </c>
@@ -13003,7 +13013,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="114" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="114" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D114">
         <v>113</v>
       </c>
@@ -13026,7 +13036,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="115" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="115" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D115">
         <v>114</v>
       </c>
@@ -13049,7 +13059,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="116" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="116" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D116">
         <v>115</v>
       </c>
@@ -13072,7 +13082,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="117" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="117" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D117">
         <v>116</v>
       </c>
@@ -13095,7 +13105,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="118" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="118" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D118">
         <v>117</v>
       </c>
@@ -13118,7 +13128,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="119" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="119" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D119">
         <v>118</v>
       </c>
@@ -13141,7 +13151,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="120" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="120" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D120">
         <v>119</v>
       </c>
@@ -13164,7 +13174,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="121" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="121" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D121">
         <v>120</v>
       </c>
@@ -13187,7 +13197,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="122" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="122" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D122">
         <v>121</v>
       </c>
@@ -13210,7 +13220,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="123" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="123" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D123">
         <v>122</v>
       </c>
@@ -13233,7 +13243,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="124" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="124" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D124">
         <v>123</v>
       </c>
@@ -13256,7 +13266,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="125" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="125" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D125">
         <v>124</v>
       </c>
@@ -13279,7 +13289,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="126" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="126" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D126">
         <v>125</v>
       </c>
@@ -13302,7 +13312,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="127" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="127" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D127">
         <v>126</v>
       </c>
@@ -13325,7 +13335,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="128" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="128" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D128">
         <v>127</v>
       </c>
@@ -13348,7 +13358,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="129" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="129" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D129">
         <v>128</v>
       </c>
@@ -13371,7 +13381,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="130" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="130" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D130">
         <v>129</v>
       </c>
@@ -13394,7 +13404,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="131" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="131" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D131">
         <v>130</v>
       </c>
@@ -13417,7 +13427,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="132" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="132" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D132">
         <v>131</v>
       </c>
@@ -13440,7 +13450,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="133" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="133" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D133">
         <v>132</v>
       </c>
@@ -13463,7 +13473,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="134" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="134" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D134">
         <v>133</v>
       </c>
@@ -13486,7 +13496,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="135" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="135" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D135">
         <v>134</v>
       </c>
@@ -13509,7 +13519,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="136" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="136" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D136">
         <v>135</v>
       </c>
@@ -13532,7 +13542,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="137" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="137" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D137">
         <v>136</v>
       </c>
@@ -13555,7 +13565,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="138" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="138" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D138">
         <v>137</v>
       </c>
@@ -13578,7 +13588,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="139" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="139" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D139">
         <v>138</v>
       </c>
@@ -13601,7 +13611,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="140" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="140" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D140">
         <v>139</v>
       </c>
@@ -13624,7 +13634,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="141" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="141" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D141">
         <v>140</v>
       </c>
@@ -13647,7 +13657,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="142" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="142" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D142">
         <v>141</v>
       </c>
@@ -13670,7 +13680,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="143" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="143" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D143">
         <v>142</v>
       </c>
@@ -13693,7 +13703,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="144" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="144" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D144">
         <v>143</v>
       </c>
@@ -13716,7 +13726,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="145" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="145" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D145">
         <v>144</v>
       </c>
@@ -13739,7 +13749,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="146" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="146" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D146">
         <v>145</v>
       </c>
@@ -13762,7 +13772,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="147" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="147" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D147">
         <v>146</v>
       </c>
@@ -13785,7 +13795,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="148" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="148" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D148">
         <v>147</v>
       </c>
@@ -13808,7 +13818,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="149" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="149" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D149">
         <v>148</v>
       </c>
@@ -13831,7 +13841,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="150" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="150" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D150">
         <v>149</v>
       </c>
@@ -13854,7 +13864,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="151" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="151" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D151">
         <v>150</v>
       </c>
@@ -13877,7 +13887,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="152" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="152" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D152">
         <v>151</v>
       </c>
@@ -13900,7 +13910,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="153" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="153" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D153">
         <v>152</v>
       </c>
@@ -13923,7 +13933,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="154" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="154" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D154">
         <v>153</v>
       </c>
@@ -13946,7 +13956,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="155" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="155" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D155">
         <v>154</v>
       </c>
@@ -13969,7 +13979,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="156" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="156" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D156">
         <v>155</v>
       </c>
@@ -13992,7 +14002,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="157" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="157" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D157">
         <v>156</v>
       </c>
@@ -14015,7 +14025,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="158" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="158" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D158">
         <v>157</v>
       </c>
@@ -14038,7 +14048,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="159" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="159" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D159">
         <v>158</v>
       </c>
@@ -14061,7 +14071,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="160" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="160" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D160">
         <v>159</v>
       </c>
@@ -14084,7 +14094,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="161" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="161" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D161">
         <v>160</v>
       </c>
@@ -14107,7 +14117,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="162" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="162" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D162">
         <v>161</v>
       </c>
@@ -14130,7 +14140,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="163" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="163" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D163">
         <v>162</v>
       </c>
@@ -14153,7 +14163,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="164" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="164" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D164">
         <v>163</v>
       </c>
@@ -14176,7 +14186,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="165" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="165" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D165">
         <v>164</v>
       </c>
@@ -14199,7 +14209,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="166" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="166" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D166">
         <v>165</v>
       </c>
@@ -14222,7 +14232,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="167" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="167" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D167">
         <v>166</v>
       </c>
@@ -14245,7 +14255,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="168" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="168" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D168">
         <v>167</v>
       </c>
@@ -14268,7 +14278,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="169" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="169" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D169">
         <v>168</v>
       </c>
@@ -14291,7 +14301,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="170" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="170" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D170">
         <v>169</v>
       </c>
@@ -14314,7 +14324,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="171" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="171" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D171">
         <v>170</v>
       </c>
@@ -14337,7 +14347,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="172" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="172" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D172">
         <v>171</v>
       </c>
@@ -14360,7 +14370,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="173" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="173" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D173">
         <v>172</v>
       </c>
@@ -14383,7 +14393,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="174" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="174" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D174">
         <v>173</v>
       </c>
@@ -14406,7 +14416,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="175" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="175" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D175">
         <v>174</v>
       </c>
@@ -14429,7 +14439,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="176" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="176" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D176">
         <v>175</v>
       </c>
@@ -14452,7 +14462,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="177" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="177" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D177">
         <v>176</v>
       </c>
@@ -14475,7 +14485,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="178" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="178" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D178">
         <v>177</v>
       </c>
@@ -14498,7 +14508,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="179" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="179" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D179">
         <v>178</v>
       </c>
@@ -14521,7 +14531,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="180" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="180" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D180">
         <v>179</v>
       </c>
@@ -14544,7 +14554,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="181" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="181" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D181">
         <v>180</v>
       </c>
@@ -14567,7 +14577,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="182" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="182" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D182">
         <v>181</v>
       </c>
@@ -14590,7 +14600,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="183" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="183" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D183">
         <v>182</v>
       </c>
@@ -14613,7 +14623,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="184" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="184" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D184">
         <v>183</v>
       </c>
@@ -14636,7 +14646,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="185" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="185" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D185">
         <v>184</v>
       </c>
@@ -14659,7 +14669,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="186" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="186" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D186">
         <v>185</v>
       </c>
@@ -14682,7 +14692,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="187" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="187" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D187">
         <v>186</v>
       </c>
@@ -14705,7 +14715,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="188" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="188" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D188">
         <v>187</v>
       </c>
@@ -14728,7 +14738,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="189" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="189" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D189">
         <v>188</v>
       </c>
@@ -14751,7 +14761,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="190" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="190" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D190">
         <v>189</v>
       </c>
@@ -14774,7 +14784,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="191" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="191" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D191">
         <v>190</v>
       </c>
@@ -14797,7 +14807,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="192" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="192" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D192">
         <v>191</v>
       </c>
@@ -14820,7 +14830,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="193" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="193" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D193">
         <v>192</v>
       </c>
@@ -14843,7 +14853,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="194" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="194" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A194">
         <v>381</v>
       </c>
@@ -14866,7 +14876,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="195" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="195" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A195">
         <v>382</v>
       </c>
@@ -14889,7 +14899,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="196" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="196" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A196">
         <v>383</v>
       </c>
@@ -14912,7 +14922,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="197" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="197" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A197">
         <v>384</v>
       </c>
@@ -14935,7 +14945,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="198" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="198" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A198">
         <v>385</v>
       </c>
@@ -14958,7 +14968,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="199" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="199" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A199">
         <v>386</v>
       </c>
@@ -14981,7 +14991,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="200" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="200" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A200">
         <v>387</v>
       </c>
@@ -15004,7 +15014,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="201" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="201" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A201">
         <v>388</v>
       </c>

--- a/焊缝统计R3_auto(1).xlsx
+++ b/焊缝统计R3_auto(1).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\hanf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83EC66D8-2652-4141-A407-ECE3D350B919}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C40BED38-FCDE-4175-AF6D-1CDC2DE23DED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4860" yWindow="4740" windowWidth="21600" windowHeight="11175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1820" yWindow="1820" windowWidth="14400" windowHeight="7450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="焊缝统计" sheetId="1" r:id="rId1"/>
@@ -20,6 +20,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">焊缝统计!$A$1:$I$419</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
+  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
@@ -723,17 +724,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:J419"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="14" style="5" customWidth="1"/>
-    <col min="3" max="3" width="23.875" style="5" customWidth="1"/>
+    <col min="3" max="3" width="23.90625" style="5" customWidth="1"/>
     <col min="4" max="8" width="14" style="5" customWidth="1"/>
-    <col min="9" max="9" width="23.75" style="5" customWidth="1"/>
-    <col min="10" max="10" width="12.5" style="5" customWidth="1"/>
+    <col min="9" max="9" width="23.7265625" style="5" customWidth="1"/>
+    <col min="10" max="10" width="12.453125" style="5" customWidth="1"/>
     <col min="11" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -763,7 +764,7 @@
       </c>
       <c r="J1" s="4"/>
     </row>
-    <row r="2" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
         <v>1</v>
       </c>
@@ -786,7 +787,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
         <v>2</v>
       </c>
@@ -809,7 +810,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
         <v>3</v>
       </c>
@@ -832,7 +833,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <v>4</v>
       </c>
@@ -855,7 +856,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <v>5</v>
       </c>
@@ -878,7 +879,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <v>6</v>
       </c>
@@ -901,7 +902,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
         <v>7</v>
       </c>
@@ -924,7 +925,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <v>8</v>
       </c>
@@ -947,7 +948,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
         <v>9</v>
       </c>
@@ -970,7 +971,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <v>10</v>
       </c>
@@ -993,7 +994,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
         <v>11</v>
       </c>
@@ -1016,7 +1017,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
         <v>12</v>
       </c>
@@ -1039,7 +1040,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
         <v>13</v>
       </c>
@@ -1062,7 +1063,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
         <v>14</v>
       </c>
@@ -1085,7 +1086,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5">
         <v>15</v>
       </c>
@@ -1108,7 +1109,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
         <v>16</v>
       </c>
@@ -1131,7 +1132,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5">
         <v>17</v>
       </c>
@@ -1154,7 +1155,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5">
         <v>18</v>
       </c>
@@ -1177,7 +1178,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5">
         <v>21</v>
       </c>
@@ -1200,7 +1201,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="21" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
         <v>22</v>
       </c>
@@ -1223,7 +1224,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="22" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5">
         <v>19</v>
       </c>
@@ -1246,7 +1247,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="23" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
         <v>20</v>
       </c>
@@ -1269,7 +1270,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="24" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5">
         <v>23</v>
       </c>
@@ -1292,7 +1293,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="25" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5">
         <v>24</v>
       </c>
@@ -1315,7 +1316,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="26" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="5">
         <v>25</v>
       </c>
@@ -1338,7 +1339,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5">
         <v>26</v>
       </c>
@@ -1361,7 +1362,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5">
         <v>27</v>
       </c>
@@ -1384,7 +1385,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5">
         <v>28</v>
       </c>
@@ -1407,7 +1408,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="5">
         <v>47</v>
       </c>
@@ -1430,7 +1431,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5">
         <v>48</v>
       </c>
@@ -1453,7 +1454,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="5">
         <v>49</v>
       </c>
@@ -1476,7 +1477,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="33" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="5">
         <v>50</v>
       </c>
@@ -1499,7 +1500,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="34" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="5">
         <v>29</v>
       </c>
@@ -1522,7 +1523,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="35" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="5">
         <v>30</v>
       </c>
@@ -1545,7 +1546,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="36" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="5">
         <v>33</v>
       </c>
@@ -1568,7 +1569,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="37" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="5">
         <v>34</v>
       </c>
@@ -1591,7 +1592,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="38" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="5">
         <v>31</v>
       </c>
@@ -1614,7 +1615,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="39" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="5">
         <v>32</v>
       </c>
@@ -1637,7 +1638,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="40" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="5">
         <v>35</v>
       </c>
@@ -1660,7 +1661,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="41" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="5">
         <v>36</v>
       </c>
@@ -1683,7 +1684,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="42" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="5">
         <v>37</v>
       </c>
@@ -1706,7 +1707,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="43" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="5">
         <v>38</v>
       </c>
@@ -1729,7 +1730,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="44" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="5">
         <v>41</v>
       </c>
@@ -1752,7 +1753,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="45" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="5">
         <v>42</v>
       </c>
@@ -1775,7 +1776,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="46" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="5">
         <v>43</v>
       </c>
@@ -1798,7 +1799,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="47" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="5">
         <v>44</v>
       </c>
@@ -1821,7 +1822,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="48" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="5">
         <v>39</v>
       </c>
@@ -1844,7 +1845,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="49" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="5">
         <v>40</v>
       </c>
@@ -1867,7 +1868,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="50" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="5">
         <v>45</v>
       </c>
@@ -1890,7 +1891,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="51" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="5">
         <v>46</v>
       </c>
@@ -1913,7 +1914,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="52" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" s="5">
         <v>53</v>
       </c>
@@ -1936,7 +1937,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="53" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" s="5">
         <v>54</v>
       </c>
@@ -1959,7 +1960,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="54" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="5">
         <v>55</v>
       </c>
@@ -1982,7 +1983,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="55" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="5">
         <v>56</v>
       </c>
@@ -2005,7 +2006,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="56" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" s="5">
         <v>63</v>
       </c>
@@ -2028,7 +2029,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="57" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" s="5">
         <v>64</v>
       </c>
@@ -2051,7 +2052,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="58" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" s="5">
         <v>65</v>
       </c>
@@ -2074,7 +2075,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="59" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" s="5">
         <v>66</v>
       </c>
@@ -2097,7 +2098,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="60" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="5">
         <v>51</v>
       </c>
@@ -2120,7 +2121,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="61" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" s="5">
         <v>52</v>
       </c>
@@ -2143,7 +2144,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="62" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="5">
         <v>61</v>
       </c>
@@ -2166,7 +2167,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="63" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" s="5">
         <v>62</v>
       </c>
@@ -2189,7 +2190,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="64" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" s="5">
         <v>57</v>
       </c>
@@ -2212,7 +2213,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="65" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" s="5">
         <v>58</v>
       </c>
@@ -2235,7 +2236,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="66" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" s="5">
         <v>67</v>
       </c>
@@ -2258,7 +2259,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="67" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" s="5">
         <v>68</v>
       </c>
@@ -2281,7 +2282,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="68" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" s="5">
         <v>59</v>
       </c>
@@ -2304,7 +2305,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="69" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" s="5">
         <v>60</v>
       </c>
@@ -2327,7 +2328,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="70" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" s="5">
         <v>69</v>
       </c>
@@ -2350,7 +2351,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="71" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" s="5">
         <v>70</v>
       </c>
@@ -2373,7 +2374,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" s="5">
         <v>71</v>
       </c>
@@ -2396,7 +2397,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" s="5">
         <v>72</v>
       </c>
@@ -2419,7 +2420,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" s="5">
         <v>73</v>
       </c>
@@ -2442,7 +2443,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" s="5">
         <v>74</v>
       </c>
@@ -2465,7 +2466,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" s="5">
         <v>77</v>
       </c>
@@ -2488,7 +2489,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" s="5">
         <v>78</v>
       </c>
@@ -2511,7 +2512,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" s="5">
         <v>91</v>
       </c>
@@ -2534,7 +2535,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" s="5">
         <v>92</v>
       </c>
@@ -2557,7 +2558,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" s="5">
         <v>81</v>
       </c>
@@ -2580,7 +2581,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" s="5">
         <v>82</v>
       </c>
@@ -2603,7 +2604,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" s="5">
         <v>85</v>
       </c>
@@ -2626,7 +2627,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" s="5">
         <v>86</v>
       </c>
@@ -2649,7 +2650,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" s="5">
         <v>97</v>
       </c>
@@ -2672,7 +2673,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" s="5">
         <v>98</v>
       </c>
@@ -2695,7 +2696,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" s="5">
         <v>83</v>
       </c>
@@ -2718,7 +2719,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" s="5">
         <v>84</v>
       </c>
@@ -2741,7 +2742,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" s="5">
         <v>95</v>
       </c>
@@ -2764,7 +2765,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" s="5">
         <v>96</v>
       </c>
@@ -2787,7 +2788,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" s="5">
         <v>75</v>
       </c>
@@ -2810,7 +2811,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" s="5">
         <v>76</v>
       </c>
@@ -2833,7 +2834,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" s="5">
         <v>79</v>
       </c>
@@ -2856,7 +2857,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" s="5">
         <v>80</v>
       </c>
@@ -2879,7 +2880,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" s="5">
         <v>89</v>
       </c>
@@ -2902,7 +2903,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" s="5">
         <v>90</v>
       </c>
@@ -2925,7 +2926,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" s="5">
         <v>93</v>
       </c>
@@ -2948,7 +2949,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="97" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" s="5">
         <v>94</v>
       </c>
@@ -2971,7 +2972,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="98" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" s="5">
         <v>87</v>
       </c>
@@ -2994,7 +2995,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="99" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" s="5">
         <v>88</v>
       </c>
@@ -3017,7 +3018,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="100" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" s="5">
         <v>101</v>
       </c>
@@ -3040,7 +3041,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="101" spans="1:9" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="101" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="5">
         <v>102</v>
       </c>
@@ -3063,7 +3064,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="102" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102" s="5">
         <v>105</v>
       </c>
@@ -3086,7 +3087,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="103" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103" s="5">
         <v>106</v>
       </c>
@@ -3109,7 +3110,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="104" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104" s="5">
         <v>113</v>
       </c>
@@ -3132,7 +3133,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="105" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105" s="5">
         <v>114</v>
       </c>
@@ -3155,7 +3156,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="106" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106" s="5">
         <v>103</v>
       </c>
@@ -3178,7 +3179,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="107" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A107" s="5">
         <v>104</v>
       </c>
@@ -3201,7 +3202,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="108" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108" s="5">
         <v>107</v>
       </c>
@@ -3224,7 +3225,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="109" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109" s="5">
         <v>108</v>
       </c>
@@ -3247,7 +3248,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="110" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110" s="5">
         <v>111</v>
       </c>
@@ -3270,7 +3271,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="111" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111" s="5">
         <v>112</v>
       </c>
@@ -3293,7 +3294,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="112" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" s="5">
         <v>99</v>
       </c>
@@ -3316,7 +3317,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" s="5">
         <v>100</v>
       </c>
@@ -3339,7 +3340,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="114" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A114" s="5">
         <v>115</v>
       </c>
@@ -3362,7 +3363,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="115" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A115" s="5">
         <v>116</v>
       </c>
@@ -3385,7 +3386,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="116" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116" s="5">
         <v>119</v>
       </c>
@@ -3408,7 +3409,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="117" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117" s="5">
         <v>120</v>
       </c>
@@ -3431,7 +3432,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="118" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118" s="5">
         <v>109</v>
       </c>
@@ -3454,7 +3455,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="119" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119" s="5">
         <v>110</v>
       </c>
@@ -3477,7 +3478,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="120" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120" s="5">
         <v>117</v>
       </c>
@@ -3500,7 +3501,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="121" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121" s="5">
         <v>118</v>
       </c>
@@ -3523,7 +3524,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="122" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A122" s="5">
         <v>121</v>
       </c>
@@ -3546,7 +3547,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="123" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A123" s="5">
         <v>122</v>
       </c>
@@ -3569,7 +3570,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="124" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="124" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" s="5">
         <v>123</v>
       </c>
@@ -3592,7 +3593,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="125" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="125" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" s="5">
         <v>124</v>
       </c>
@@ -3615,7 +3616,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="126" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="126" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" s="5">
         <v>125</v>
       </c>
@@ -3638,7 +3639,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="127" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="127" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" s="5">
         <v>126</v>
       </c>
@@ -3661,7 +3662,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="128" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="128" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" s="5">
         <v>127</v>
       </c>
@@ -3684,7 +3685,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="129" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="129" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" s="5">
         <v>128</v>
       </c>
@@ -3707,7 +3708,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="130" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="130" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" s="5">
         <v>129</v>
       </c>
@@ -3730,7 +3731,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="131" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="131" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" s="5">
         <v>130</v>
       </c>
@@ -3753,7 +3754,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="132" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="132" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" s="5">
         <v>131</v>
       </c>
@@ -3776,7 +3777,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="133" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="133" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" s="5">
         <v>132</v>
       </c>
@@ -3799,7 +3800,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="134" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="134" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" s="5">
         <v>133</v>
       </c>
@@ -3822,7 +3823,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="135" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="135" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" s="5">
         <v>134</v>
       </c>
@@ -3845,7 +3846,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="136" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="136" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" s="5">
         <v>145</v>
       </c>
@@ -3868,7 +3869,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="137" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="137" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" s="5">
         <v>146</v>
       </c>
@@ -3891,7 +3892,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="138" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="138" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" s="5">
         <v>141</v>
       </c>
@@ -3914,7 +3915,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="139" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="139" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" s="5">
         <v>142</v>
       </c>
@@ -3937,7 +3938,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="140" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="140" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" s="5">
         <v>143</v>
       </c>
@@ -3960,7 +3961,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="141" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="141" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" s="5">
         <v>144</v>
       </c>
@@ -3983,7 +3984,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="142" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="142" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" s="5">
         <v>135</v>
       </c>
@@ -4006,7 +4007,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="143" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="143" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" s="5">
         <v>136</v>
       </c>
@@ -4029,7 +4030,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="144" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="144" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" s="5">
         <v>137</v>
       </c>
@@ -4052,7 +4053,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="145" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="145" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145" s="5">
         <v>138</v>
       </c>
@@ -4075,7 +4076,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="146" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="146" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" s="5">
         <v>139</v>
       </c>
@@ -4098,7 +4099,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="147" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="147" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" s="5">
         <v>140</v>
       </c>
@@ -4121,7 +4122,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="148" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="148" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148" s="5">
         <v>171</v>
       </c>
@@ -4144,7 +4145,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="149" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="149" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149" s="5">
         <v>172</v>
       </c>
@@ -4167,7 +4168,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="150" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="150" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150" s="5">
         <v>173</v>
       </c>
@@ -4190,7 +4191,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="151" spans="1:9" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="151" spans="1:9" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="5">
         <v>174</v>
       </c>
@@ -4213,7 +4214,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="152" spans="1:9" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="152" spans="1:9" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="5">
         <v>175</v>
       </c>
@@ -4236,7 +4237,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="153" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="153" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153" s="5">
         <v>176</v>
       </c>
@@ -4259,7 +4260,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="154" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="154" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154" s="5">
         <v>177</v>
       </c>
@@ -4282,7 +4283,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="155" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="155" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155" s="5">
         <v>178</v>
       </c>
@@ -4305,7 +4306,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="156" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="156" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156" s="5">
         <v>179</v>
       </c>
@@ -4328,7 +4329,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="157" spans="1:9" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="157" spans="1:9" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="5">
         <v>180</v>
       </c>
@@ -4351,7 +4352,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="158" spans="1:9" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="158" spans="1:9" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="5">
         <v>181</v>
       </c>
@@ -4374,7 +4375,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="159" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="159" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159" s="5">
         <v>182</v>
       </c>
@@ -4397,7 +4398,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="160" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="160" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160" s="5">
         <v>165</v>
       </c>
@@ -4420,7 +4421,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="161" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="161" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161" s="5">
         <v>166</v>
       </c>
@@ -4443,7 +4444,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="162" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="162" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162" s="5">
         <v>167</v>
       </c>
@@ -4466,7 +4467,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="163" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="163" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163" s="5">
         <v>168</v>
       </c>
@@ -4489,7 +4490,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="164" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="164" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164" s="5">
         <v>169</v>
       </c>
@@ -4512,7 +4513,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="165" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="165" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165" s="5">
         <v>170</v>
       </c>
@@ -4535,7 +4536,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="166" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="166" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A166" s="5">
         <v>147</v>
       </c>
@@ -4558,7 +4559,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="167" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="167" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167" s="5">
         <v>148</v>
       </c>
@@ -4581,7 +4582,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="168" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="168" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168" s="5">
         <v>149</v>
       </c>
@@ -4604,7 +4605,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="169" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="169" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A169" s="5">
         <v>150</v>
       </c>
@@ -4627,7 +4628,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="170" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="170" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A170" s="5">
         <v>151</v>
       </c>
@@ -4650,7 +4651,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="171" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="171" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A171" s="5">
         <v>152</v>
       </c>
@@ -4673,7 +4674,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="172" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="172" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A172" s="5">
         <v>153</v>
       </c>
@@ -4696,7 +4697,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="173" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="173" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A173" s="5">
         <v>154</v>
       </c>
@@ -4719,7 +4720,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="174" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="174" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A174" s="5">
         <v>155</v>
       </c>
@@ -4742,7 +4743,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="175" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="175" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175" s="5">
         <v>156</v>
       </c>
@@ -4765,7 +4766,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="176" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="176" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A176" s="5">
         <v>157</v>
       </c>
@@ -4788,7 +4789,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="177" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="177" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177" s="5">
         <v>158</v>
       </c>
@@ -4811,7 +4812,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="178" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="178" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A178" s="5">
         <v>159</v>
       </c>
@@ -4834,7 +4835,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="179" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="179" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A179" s="5">
         <v>160</v>
       </c>
@@ -4857,7 +4858,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="180" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="180" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A180" s="5">
         <v>161</v>
       </c>
@@ -4880,7 +4881,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="181" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="181" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A181" s="5">
         <v>162</v>
       </c>
@@ -4903,7 +4904,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="182" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="182" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A182" s="5">
         <v>163</v>
       </c>
@@ -4926,7 +4927,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="183" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="183" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A183" s="5">
         <v>164</v>
       </c>
@@ -4949,7 +4950,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="184" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="184" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A184" s="5">
         <v>183</v>
       </c>
@@ -4972,7 +4973,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="185" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="185" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A185" s="5">
         <v>184</v>
       </c>
@@ -4995,7 +4996,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="186" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="186" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A186" s="5">
         <v>185</v>
       </c>
@@ -5018,7 +5019,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="187" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="187" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A187" s="5">
         <v>186</v>
       </c>
@@ -5041,7 +5042,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="188" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="188" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A188" s="5">
         <v>187</v>
       </c>
@@ -5064,7 +5065,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="189" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="189" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A189" s="5">
         <v>188</v>
       </c>
@@ -5087,7 +5088,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="190" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="190" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A190" s="5">
         <v>189</v>
       </c>
@@ -5110,7 +5111,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="191" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="191" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A191" s="5">
         <v>190</v>
       </c>
@@ -5133,7 +5134,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="192" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="192" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A192" s="5">
         <v>191</v>
       </c>
@@ -5156,7 +5157,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="193" spans="1:8" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="193" spans="1:8" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="5">
         <v>192</v>
       </c>
@@ -5179,7 +5180,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="194" spans="1:8" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="194" spans="1:8" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="5">
         <v>193</v>
       </c>
@@ -5202,7 +5203,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="195" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="195" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A195" s="5">
         <v>194</v>
       </c>
@@ -5225,7 +5226,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="196" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="196" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A196" s="5">
         <v>195</v>
       </c>
@@ -5248,7 +5249,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="197" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="197" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A197" s="5">
         <v>196</v>
       </c>
@@ -5271,7 +5272,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="198" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="198" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A198" s="5">
         <v>197</v>
       </c>
@@ -5294,7 +5295,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="199" spans="1:8" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="199" spans="1:8" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="5">
         <v>198</v>
       </c>
@@ -5317,7 +5318,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="200" spans="1:8" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="200" spans="1:8" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="5">
         <v>199</v>
       </c>
@@ -5340,7 +5341,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="201" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="201" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A201" s="5">
         <v>200</v>
       </c>
@@ -5363,7 +5364,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="202" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="202" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A202" s="5">
         <v>201</v>
       </c>
@@ -5386,7 +5387,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="203" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="203" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A203" s="5">
         <v>202</v>
       </c>
@@ -5409,7 +5410,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="204" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="204" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A204" s="5">
         <v>203</v>
       </c>
@@ -5432,7 +5433,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="205" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="205" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A205" s="5">
         <v>204</v>
       </c>
@@ -5455,7 +5456,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="206" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="206" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A206" s="5">
         <v>205</v>
       </c>
@@ -5478,7 +5479,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="207" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="207" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A207" s="5">
         <v>206</v>
       </c>
@@ -5501,7 +5502,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="208" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="208" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A208" s="5">
         <v>207</v>
       </c>
@@ -5524,7 +5525,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="209" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="209" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A209" s="5">
         <v>208</v>
       </c>
@@ -5547,7 +5548,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="210" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="210" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A210" s="5">
         <v>209</v>
       </c>
@@ -5570,7 +5571,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="211" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="211" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A211" s="5">
         <v>210</v>
       </c>
@@ -5593,7 +5594,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="212" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="212" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A212" s="5">
         <v>211</v>
       </c>
@@ -5616,7 +5617,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="213" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="213" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A213" s="5">
         <v>212</v>
       </c>
@@ -5639,7 +5640,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="214" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="214" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A214" s="5">
         <v>213</v>
       </c>
@@ -5662,7 +5663,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="215" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="215" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A215" s="5">
         <v>214</v>
       </c>
@@ -5685,7 +5686,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="216" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="216" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A216" s="5">
         <v>215</v>
       </c>
@@ -5708,7 +5709,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="217" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="217" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A217" s="5">
         <v>216</v>
       </c>
@@ -5731,7 +5732,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="218" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="218" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A218" s="5">
         <v>217</v>
       </c>
@@ -5754,7 +5755,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="219" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="219" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A219" s="5">
         <v>218</v>
       </c>
@@ -5777,7 +5778,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="220" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="220" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A220" s="5">
         <v>219</v>
       </c>
@@ -5800,7 +5801,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="221" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="221" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A221" s="5">
         <v>220</v>
       </c>
@@ -5823,7 +5824,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="222" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="222" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A222" s="5">
         <v>221</v>
       </c>
@@ -5846,7 +5847,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="223" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="223" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A223" s="5">
         <v>222</v>
       </c>
@@ -5869,7 +5870,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="224" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="224" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A224" s="5">
         <v>223</v>
       </c>
@@ -5892,7 +5893,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="225" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="225" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A225" s="5">
         <v>224</v>
       </c>
@@ -5915,7 +5916,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="226" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="226" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A226" s="5">
         <v>243</v>
       </c>
@@ -5938,7 +5939,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="227" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="227" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A227" s="5">
         <v>244</v>
       </c>
@@ -5961,7 +5962,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="228" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="228" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A228" s="5">
         <v>247</v>
       </c>
@@ -5984,7 +5985,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="229" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="229" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A229" s="5">
         <v>248</v>
       </c>
@@ -6007,7 +6008,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="230" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="230" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A230" s="5">
         <v>251</v>
       </c>
@@ -6030,7 +6031,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="231" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="231" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A231" s="5">
         <v>252</v>
       </c>
@@ -6053,7 +6054,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="232" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="232" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A232" s="5">
         <v>245</v>
       </c>
@@ -6076,7 +6077,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="233" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="233" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A233" s="5">
         <v>246</v>
       </c>
@@ -6099,7 +6100,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="234" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="234" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A234" s="5">
         <v>249</v>
       </c>
@@ -6122,7 +6123,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="235" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="235" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A235" s="5">
         <v>250</v>
       </c>
@@ -6145,7 +6146,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="236" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="236" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A236" s="5">
         <v>237</v>
       </c>
@@ -6168,7 +6169,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="237" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="237" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A237" s="5">
         <v>238</v>
       </c>
@@ -6191,7 +6192,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="238" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="238" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A238" s="5">
         <v>239</v>
       </c>
@@ -6214,7 +6215,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="239" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="239" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A239" s="5">
         <v>240</v>
       </c>
@@ -6237,7 +6238,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="240" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="240" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A240" s="5">
         <v>241</v>
       </c>
@@ -6260,7 +6261,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="241" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="241" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A241" s="5">
         <v>242</v>
       </c>
@@ -6283,7 +6284,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="242" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="242" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A242" s="5">
         <v>225</v>
       </c>
@@ -6306,7 +6307,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="243" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="243" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A243" s="5">
         <v>226</v>
       </c>
@@ -6329,7 +6330,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="244" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="244" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A244" s="5">
         <v>227</v>
       </c>
@@ -6352,7 +6353,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="245" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="245" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A245" s="5">
         <v>228</v>
       </c>
@@ -6375,7 +6376,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="246" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="246" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A246" s="5">
         <v>229</v>
       </c>
@@ -6398,7 +6399,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="247" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="247" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A247" s="5">
         <v>230</v>
       </c>
@@ -6421,7 +6422,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="248" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="248" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A248" s="5">
         <v>233</v>
       </c>
@@ -6444,7 +6445,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="249" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="249" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A249" s="5">
         <v>234</v>
       </c>
@@ -6467,7 +6468,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="250" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="250" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A250" s="5">
         <v>235</v>
       </c>
@@ -6490,7 +6491,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="251" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="251" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A251" s="5">
         <v>236</v>
       </c>
@@ -6513,7 +6514,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="252" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="252" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A252" s="5">
         <v>231</v>
       </c>
@@ -6536,7 +6537,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="253" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="253" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A253" s="5">
         <v>232</v>
       </c>
@@ -6559,7 +6560,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="254" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="254" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A254" s="5">
         <v>253</v>
       </c>
@@ -6582,7 +6583,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="255" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="255" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A255" s="5">
         <v>254</v>
       </c>
@@ -6605,7 +6606,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="256" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="256" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A256" s="5">
         <v>255</v>
       </c>
@@ -6628,7 +6629,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="257" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="257" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A257" s="5">
         <v>256</v>
       </c>
@@ -6651,7 +6652,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="258" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="258" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A258" s="5">
         <v>257</v>
       </c>
@@ -6674,7 +6675,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="259" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="259" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A259" s="5">
         <v>258</v>
       </c>
@@ -6697,7 +6698,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="260" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="260" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A260" s="5">
         <v>259</v>
       </c>
@@ -6720,7 +6721,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="261" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="261" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A261" s="5">
         <v>260</v>
       </c>
@@ -6743,7 +6744,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="262" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="262" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A262" s="5">
         <v>261</v>
       </c>
@@ -6766,7 +6767,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="263" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="263" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A263" s="5">
         <v>262</v>
       </c>
@@ -6789,7 +6790,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="264" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="264" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A264" s="5">
         <v>263</v>
       </c>
@@ -6812,7 +6813,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="265" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="265" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A265" s="5">
         <v>264</v>
       </c>
@@ -6835,7 +6836,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="266" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="266" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A266" s="5">
         <v>265</v>
       </c>
@@ -6858,7 +6859,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="267" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="267" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A267" s="5">
         <v>266</v>
       </c>
@@ -6881,7 +6882,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="268" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="268" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A268" s="5">
         <v>267</v>
       </c>
@@ -6904,7 +6905,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="269" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="269" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A269" s="5">
         <v>268</v>
       </c>
@@ -6927,7 +6928,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="270" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="270" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A270" s="5">
         <v>269</v>
       </c>
@@ -6950,7 +6951,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="271" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="271" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A271" s="5">
         <v>270</v>
       </c>
@@ -6973,7 +6974,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="272" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="272" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A272" s="5">
         <v>271</v>
       </c>
@@ -6996,7 +6997,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="273" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="273" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A273" s="5">
         <v>272</v>
       </c>
@@ -7019,7 +7020,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="274" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="274" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A274" s="5">
         <v>273</v>
       </c>
@@ -7042,7 +7043,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="275" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="275" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A275" s="5">
         <v>274</v>
       </c>
@@ -7065,7 +7066,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="276" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="276" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A276" s="5">
         <v>275</v>
       </c>
@@ -7088,7 +7089,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="277" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="277" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A277" s="5">
         <v>276</v>
       </c>
@@ -7111,7 +7112,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="278" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="278" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A278" s="5">
         <v>277</v>
       </c>
@@ -7134,7 +7135,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="279" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="279" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A279" s="5">
         <v>278</v>
       </c>
@@ -7157,7 +7158,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="280" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="280" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A280" s="5">
         <v>279</v>
       </c>
@@ -7180,7 +7181,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="281" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="281" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A281" s="5">
         <v>280</v>
       </c>
@@ -7203,7 +7204,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="282" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="282" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A282" s="5">
         <v>281</v>
       </c>
@@ -7226,7 +7227,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="283" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="283" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A283" s="5">
         <v>282</v>
       </c>
@@ -7249,7 +7250,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="284" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="284" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A284" s="5">
         <v>283</v>
       </c>
@@ -7272,7 +7273,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="285" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="285" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A285" s="5">
         <v>284</v>
       </c>
@@ -7295,7 +7296,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="286" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="286" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A286" s="5">
         <v>285</v>
       </c>
@@ -7318,7 +7319,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="287" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="287" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A287" s="5">
         <v>286</v>
       </c>
@@ -7341,7 +7342,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="288" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="288" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A288" s="5">
         <v>287</v>
       </c>
@@ -7364,7 +7365,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="289" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="289" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A289" s="5">
         <v>288</v>
       </c>
@@ -7387,7 +7388,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="290" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="290" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A290" s="5">
         <v>289</v>
       </c>
@@ -7410,7 +7411,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="291" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="291" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A291" s="5">
         <v>290</v>
       </c>
@@ -7433,7 +7434,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="292" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="292" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A292" s="5">
         <v>291</v>
       </c>
@@ -7456,7 +7457,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="293" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="293" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A293" s="5">
         <v>292</v>
       </c>
@@ -7479,7 +7480,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="294" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="294" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A294" s="5">
         <v>293</v>
       </c>
@@ -7502,7 +7503,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="295" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="295" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A295" s="5">
         <v>294</v>
       </c>
@@ -7525,7 +7526,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="296" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="296" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A296" s="5">
         <v>295</v>
       </c>
@@ -7548,7 +7549,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="297" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="297" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A297" s="5">
         <v>296</v>
       </c>
@@ -7571,7 +7572,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="298" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="298" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A298" s="5">
         <v>297</v>
       </c>
@@ -7594,7 +7595,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="299" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="299" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A299" s="5">
         <v>298</v>
       </c>
@@ -7617,7 +7618,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="300" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="300" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A300" s="5">
         <v>299</v>
       </c>
@@ -7640,7 +7641,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="301" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="301" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A301" s="5">
         <v>300</v>
       </c>
@@ -7663,7 +7664,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="302" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="302" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A302" s="5">
         <v>301</v>
       </c>
@@ -7686,7 +7687,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="303" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="303" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A303" s="5">
         <v>302</v>
       </c>
@@ -7709,7 +7710,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="304" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="304" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A304" s="5">
         <v>303</v>
       </c>
@@ -7732,7 +7733,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="305" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="305" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A305" s="5">
         <v>304</v>
       </c>
@@ -7755,7 +7756,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="306" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="306" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A306" s="5">
         <v>305</v>
       </c>
@@ -7778,7 +7779,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="307" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="307" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A307" s="5">
         <v>306</v>
       </c>
@@ -7801,7 +7802,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="308" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="308" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A308" s="5">
         <v>307</v>
       </c>
@@ -7824,7 +7825,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="309" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="309" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A309" s="5">
         <v>308</v>
       </c>
@@ -7847,7 +7848,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="310" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="310" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A310" s="5">
         <v>309</v>
       </c>
@@ -7870,7 +7871,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="311" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="311" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A311" s="5">
         <v>310</v>
       </c>
@@ -7893,7 +7894,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="312" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="312" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A312" s="5">
         <v>311</v>
       </c>
@@ -7916,7 +7917,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="313" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="313" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A313" s="5">
         <v>312</v>
       </c>
@@ -7939,7 +7940,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="314" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="314" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A314" s="5">
         <v>313</v>
       </c>
@@ -7962,7 +7963,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="315" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="315" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A315" s="5">
         <v>314</v>
       </c>
@@ -7985,7 +7986,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="316" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="316" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A316" s="5">
         <v>315</v>
       </c>
@@ -8008,7 +8009,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="317" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="317" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A317" s="5">
         <v>316</v>
       </c>
@@ -8031,7 +8032,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="318" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="318" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A318" s="5">
         <v>317</v>
       </c>
@@ -8054,7 +8055,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="319" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="319" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A319" s="5">
         <v>318</v>
       </c>
@@ -8077,7 +8078,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="320" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="320" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A320" s="5">
         <v>319</v>
       </c>
@@ -8100,7 +8101,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="321" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="321" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A321" s="5">
         <v>320</v>
       </c>
@@ -8123,7 +8124,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="322" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="322" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A322" s="5">
         <v>321</v>
       </c>
@@ -8146,7 +8147,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="323" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="323" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A323" s="5">
         <v>322</v>
       </c>
@@ -8169,7 +8170,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="324" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="324" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A324" s="5">
         <v>323</v>
       </c>
@@ -8192,7 +8193,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="325" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="325" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A325" s="5">
         <v>324</v>
       </c>
@@ -8215,7 +8216,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="326" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="326" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A326" s="5">
         <v>325</v>
       </c>
@@ -8238,7 +8239,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="327" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="327" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A327" s="5">
         <v>326</v>
       </c>
@@ -8261,7 +8262,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="328" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="328" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A328" s="5">
         <v>327</v>
       </c>
@@ -8284,7 +8285,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="329" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="329" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A329" s="5">
         <v>328</v>
       </c>
@@ -8307,7 +8308,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="330" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="330" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A330" s="5">
         <v>329</v>
       </c>
@@ -8330,7 +8331,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="331" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="331" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A331" s="5">
         <v>330</v>
       </c>
@@ -8353,7 +8354,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="332" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="332" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A332" s="5">
         <v>331</v>
       </c>
@@ -8376,7 +8377,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="333" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="333" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A333" s="5">
         <v>332</v>
       </c>
@@ -8399,7 +8400,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="334" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="334" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A334" s="5">
         <v>333</v>
       </c>
@@ -8422,7 +8423,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="335" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="335" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A335" s="5">
         <v>334</v>
       </c>
@@ -8445,7 +8446,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="336" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="336" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A336" s="5">
         <v>335</v>
       </c>
@@ -8468,7 +8469,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="337" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="337" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A337" s="5">
         <v>336</v>
       </c>
@@ -8491,7 +8492,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="338" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="338" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A338" s="5">
         <v>337</v>
       </c>
@@ -8514,7 +8515,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="339" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="339" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A339" s="5">
         <v>338</v>
       </c>
@@ -8537,7 +8538,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="340" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="340" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A340" s="5">
         <v>339</v>
       </c>
@@ -8560,7 +8561,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="341" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="341" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A341" s="5">
         <v>340</v>
       </c>
@@ -8583,7 +8584,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="342" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="342" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A342" s="5">
         <v>341</v>
       </c>
@@ -8606,7 +8607,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="343" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="343" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A343" s="5">
         <v>342</v>
       </c>
@@ -8629,7 +8630,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="344" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="344" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A344" s="5">
         <v>343</v>
       </c>
@@ -8652,7 +8653,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="345" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="345" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A345" s="5">
         <v>344</v>
       </c>
@@ -8675,7 +8676,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="346" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="346" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A346" s="5">
         <v>345</v>
       </c>
@@ -8698,7 +8699,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="347" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="347" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A347" s="5">
         <v>346</v>
       </c>
@@ -8721,7 +8722,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="348" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="348" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A348" s="5">
         <v>347</v>
       </c>
@@ -8744,7 +8745,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="349" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="349" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A349" s="5">
         <v>348</v>
       </c>
@@ -8767,7 +8768,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="350" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="350" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A350" s="5">
         <v>349</v>
       </c>
@@ -8790,7 +8791,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="351" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="351" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A351" s="5">
         <v>350</v>
       </c>
@@ -8813,7 +8814,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="352" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="352" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A352" s="5">
         <v>351</v>
       </c>
@@ -8836,7 +8837,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="353" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="353" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A353" s="5">
         <v>352</v>
       </c>
@@ -8859,7 +8860,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="354" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="354" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A354" s="5">
         <v>353</v>
       </c>
@@ -8882,7 +8883,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="355" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="355" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A355" s="5">
         <v>354</v>
       </c>
@@ -8905,7 +8906,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="356" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="356" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A356" s="5">
         <v>355</v>
       </c>
@@ -8928,7 +8929,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="357" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="357" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A357" s="5">
         <v>356</v>
       </c>
@@ -8951,7 +8952,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="358" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="358" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A358" s="5">
         <v>357</v>
       </c>
@@ -8974,7 +8975,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="359" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="359" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A359" s="5">
         <v>358</v>
       </c>
@@ -8997,7 +8998,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="360" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="360" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A360" s="5">
         <v>359</v>
       </c>
@@ -9020,7 +9021,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="361" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="361" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A361" s="5">
         <v>360</v>
       </c>
@@ -9043,7 +9044,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="362" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="362" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A362" s="5">
         <v>361</v>
       </c>
@@ -9066,7 +9067,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="363" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="363" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A363" s="5">
         <v>362</v>
       </c>
@@ -9089,7 +9090,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="364" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="364" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A364" s="5">
         <v>363</v>
       </c>
@@ -9112,7 +9113,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="365" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="365" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A365" s="5">
         <v>364</v>
       </c>
@@ -9135,7 +9136,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="366" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="366" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A366" s="5">
         <v>365</v>
       </c>
@@ -9158,7 +9159,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="367" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="367" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A367" s="5">
         <v>366</v>
       </c>
@@ -9181,7 +9182,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="368" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="368" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A368" s="5">
         <v>367</v>
       </c>
@@ -9204,7 +9205,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="369" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="369" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A369" s="5">
         <v>368</v>
       </c>
@@ -9227,7 +9228,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="370" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="370" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A370" s="5">
         <v>369</v>
       </c>
@@ -9250,7 +9251,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="371" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="371" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A371" s="5">
         <v>370</v>
       </c>
@@ -9273,7 +9274,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="372" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="372" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A372" s="5">
         <v>371</v>
       </c>
@@ -9296,7 +9297,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="373" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="373" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A373" s="5">
         <v>372</v>
       </c>
@@ -9319,7 +9320,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="374" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="374" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A374" s="5">
         <v>373</v>
       </c>
@@ -9342,7 +9343,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="375" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="375" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A375" s="5">
         <v>374</v>
       </c>
@@ -9365,7 +9366,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="376" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="376" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A376" s="5">
         <v>375</v>
       </c>
@@ -9388,7 +9389,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="377" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="377" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A377" s="5">
         <v>376</v>
       </c>
@@ -9411,7 +9412,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="378" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="378" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A378" s="5">
         <v>377</v>
       </c>
@@ -9434,7 +9435,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="379" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="379" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A379" s="5">
         <v>378</v>
       </c>
@@ -9457,7 +9458,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="380" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="380" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A380" s="5">
         <v>379</v>
       </c>
@@ -9480,7 +9481,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="381" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="381" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A381" s="5">
         <v>380</v>
       </c>
@@ -9503,7 +9504,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="382" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="382" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A382" s="5">
         <v>381</v>
       </c>
@@ -9526,7 +9527,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="383" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="383" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A383" s="5">
         <v>382</v>
       </c>
@@ -9549,7 +9550,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="384" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="384" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A384" s="5">
         <v>383</v>
       </c>
@@ -9572,7 +9573,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="385" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="385" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A385" s="5">
         <v>384</v>
       </c>
@@ -9595,7 +9596,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="386" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="386" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A386" s="5">
         <v>385</v>
       </c>
@@ -9618,7 +9619,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="387" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="387" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A387" s="5">
         <v>386</v>
       </c>
@@ -9641,7 +9642,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="388" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="388" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A388" s="5">
         <v>387</v>
       </c>
@@ -9664,7 +9665,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="389" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="389" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A389" s="5">
         <v>388</v>
       </c>
@@ -9687,7 +9688,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="390" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="390" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A390" s="5">
         <v>389</v>
       </c>
@@ -9710,7 +9711,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="391" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="391" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A391" s="5">
         <v>390</v>
       </c>
@@ -9733,7 +9734,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="392" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="392" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A392" s="5">
         <v>391</v>
       </c>
@@ -9756,7 +9757,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="393" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="393" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A393" s="5">
         <v>392</v>
       </c>
@@ -9779,7 +9780,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="394" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="394" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A394" s="5">
         <v>393</v>
       </c>
@@ -9802,7 +9803,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="395" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="395" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A395" s="5">
         <v>394</v>
       </c>
@@ -9825,7 +9826,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="396" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="396" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A396" s="5">
         <v>395</v>
       </c>
@@ -9848,7 +9849,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="397" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="397" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A397" s="5">
         <v>396</v>
       </c>
@@ -9871,7 +9872,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="398" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="398" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A398" s="5">
         <v>397</v>
       </c>
@@ -9894,7 +9895,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="399" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="399" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A399" s="5">
         <v>398</v>
       </c>
@@ -9917,7 +9918,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="400" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="400" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A400" s="5">
         <v>399</v>
       </c>
@@ -9940,7 +9941,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="401" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="401" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A401" s="5">
         <v>400</v>
       </c>
@@ -9963,7 +9964,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="402" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="402" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A402" s="5">
         <v>401</v>
       </c>
@@ -9986,7 +9987,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="403" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="403" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A403" s="5">
         <v>402</v>
       </c>
@@ -10009,7 +10010,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="404" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="404" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A404" s="5">
         <v>403</v>
       </c>
@@ -10032,7 +10033,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="405" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="405" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A405" s="5">
         <v>404</v>
       </c>
@@ -10055,7 +10056,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="406" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="406" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A406" s="5">
         <v>405</v>
       </c>
@@ -10078,7 +10079,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="407" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="407" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A407" s="5">
         <v>406</v>
       </c>
@@ -10101,7 +10102,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="408" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="408" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A408" s="5">
         <v>407</v>
       </c>
@@ -10124,7 +10125,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="409" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="409" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A409" s="5">
         <v>408</v>
       </c>
@@ -10147,7 +10148,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="410" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="410" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A410" s="5">
         <v>409</v>
       </c>
@@ -10170,7 +10171,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="411" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="411" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A411" s="5">
         <v>410</v>
       </c>
@@ -10193,7 +10194,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="412" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="412" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A412" s="5">
         <v>411</v>
       </c>
@@ -10216,7 +10217,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="413" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="413" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A413" s="5">
         <v>412</v>
       </c>
@@ -10239,7 +10240,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="414" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="414" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A414" s="5">
         <v>413</v>
       </c>
@@ -10262,7 +10263,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="415" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="415" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A415" s="5">
         <v>414</v>
       </c>
@@ -10285,7 +10286,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="416" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="416" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A416" s="5">
         <v>415</v>
       </c>
@@ -10308,7 +10309,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="417" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="417" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A417" s="5">
         <v>416</v>
       </c>
@@ -10331,7 +10332,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="418" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="418" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A418" s="5">
         <v>417</v>
       </c>
@@ -10354,7 +10355,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="419" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="419" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A419" s="5">
         <v>418</v>
       </c>
@@ -10381,7 +10382,7 @@
   <autoFilter ref="A1:I419" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <filterColumn colId="7">
       <filters>
-        <filter val="BE022"/>
+        <filter val="BE023"/>
       </filters>
     </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A52:I71">
@@ -10397,15 +10398,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:K201"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="1"/>
     <col min="2" max="2" width="40" customWidth="1"/>
-    <col min="5" max="5" width="16.875" customWidth="1"/>
-    <col min="11" max="11" width="23.375" customWidth="1"/>
+    <col min="5" max="5" width="16.90625" customWidth="1"/>
+    <col min="11" max="11" width="23.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>46</v>
       </c>
@@ -10437,7 +10438,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D2">
         <v>1</v>
       </c>
@@ -10460,7 +10461,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D3">
         <v>2</v>
       </c>
@@ -10483,7 +10484,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D4">
         <v>3</v>
       </c>
@@ -10506,7 +10507,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D5">
         <v>4</v>
       </c>
@@ -10529,7 +10530,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D6">
         <v>5</v>
       </c>
@@ -10552,7 +10553,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D7">
         <v>6</v>
       </c>
@@ -10575,7 +10576,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D8">
         <v>7</v>
       </c>
@@ -10598,7 +10599,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D9">
         <v>8</v>
       </c>
@@ -10621,7 +10622,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D10">
         <v>9</v>
       </c>
@@ -10644,7 +10645,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D11">
         <v>10</v>
       </c>
@@ -10667,7 +10668,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D12">
         <v>11</v>
       </c>
@@ -10690,7 +10691,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D13">
         <v>12</v>
       </c>
@@ -10713,7 +10714,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D14">
         <v>13</v>
       </c>
@@ -10736,7 +10737,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D15">
         <v>14</v>
       </c>
@@ -10759,7 +10760,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D16">
         <v>15</v>
       </c>
@@ -10782,7 +10783,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="17" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D17">
         <v>16</v>
       </c>
@@ -10805,7 +10806,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="18" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D18">
         <v>17</v>
       </c>
@@ -10828,7 +10829,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="19" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D19">
         <v>18</v>
       </c>
@@ -10851,7 +10852,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="20" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D20">
         <v>19</v>
       </c>
@@ -10874,7 +10875,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="21" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="21" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D21">
         <v>20</v>
       </c>
@@ -10897,7 +10898,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="22" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="22" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D22">
         <v>21</v>
       </c>
@@ -10920,7 +10921,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="23" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="23" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D23">
         <v>22</v>
       </c>
@@ -10943,7 +10944,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="24" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="24" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D24">
         <v>23</v>
       </c>
@@ -10966,7 +10967,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="25" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="25" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D25">
         <v>24</v>
       </c>
@@ -10989,7 +10990,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="26" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="26" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D26">
         <v>25</v>
       </c>
@@ -11012,7 +11013,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="27" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="27" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D27">
         <v>26</v>
       </c>
@@ -11035,7 +11036,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="28" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="28" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D28">
         <v>27</v>
       </c>
@@ -11058,7 +11059,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="29" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="29" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D29">
         <v>28</v>
       </c>
@@ -11081,7 +11082,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="30" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="30" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D30">
         <v>29</v>
       </c>
@@ -11104,7 +11105,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="31" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="31" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D31">
         <v>30</v>
       </c>
@@ -11127,7 +11128,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="32" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="32" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D32">
         <v>31</v>
       </c>
@@ -11150,7 +11151,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="33" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="33" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D33">
         <v>32</v>
       </c>
@@ -11173,7 +11174,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="34" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="34" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D34">
         <v>33</v>
       </c>
@@ -11196,7 +11197,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="35" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="35" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D35">
         <v>34</v>
       </c>
@@ -11219,7 +11220,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="36" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="36" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D36">
         <v>35</v>
       </c>
@@ -11242,7 +11243,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="37" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="37" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D37">
         <v>36</v>
       </c>
@@ -11265,7 +11266,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="38" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="38" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D38">
         <v>37</v>
       </c>
@@ -11288,7 +11289,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="39" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="39" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D39">
         <v>38</v>
       </c>
@@ -11311,7 +11312,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="40" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="40" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D40">
         <v>39</v>
       </c>
@@ -11334,7 +11335,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="41" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="41" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D41">
         <v>40</v>
       </c>
@@ -11357,7 +11358,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="42" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="42" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D42">
         <v>41</v>
       </c>
@@ -11380,7 +11381,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="43" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="43" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D43">
         <v>42</v>
       </c>
@@ -11403,7 +11404,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="44" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="44" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D44">
         <v>43</v>
       </c>
@@ -11426,7 +11427,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="45" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="45" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D45">
         <v>44</v>
       </c>
@@ -11449,7 +11450,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="46" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="46" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D46">
         <v>45</v>
       </c>
@@ -11472,7 +11473,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="47" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="47" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D47">
         <v>46</v>
       </c>
@@ -11495,7 +11496,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="48" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="48" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D48">
         <v>47</v>
       </c>
@@ -11518,7 +11519,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="49" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="49" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D49">
         <v>48</v>
       </c>
@@ -11541,7 +11542,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="50" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="50" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D50">
         <v>49</v>
       </c>
@@ -11564,7 +11565,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="51" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="51" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D51">
         <v>50</v>
       </c>
@@ -11587,7 +11588,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="52" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="52" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D52">
         <v>51</v>
       </c>
@@ -11610,7 +11611,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="53" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="53" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D53">
         <v>52</v>
       </c>
@@ -11633,7 +11634,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="54" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="54" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D54">
         <v>53</v>
       </c>
@@ -11656,7 +11657,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="55" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="55" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D55">
         <v>54</v>
       </c>
@@ -11679,7 +11680,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="56" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="56" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D56">
         <v>55</v>
       </c>
@@ -11702,7 +11703,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="57" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="57" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D57">
         <v>56</v>
       </c>
@@ -11725,7 +11726,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="58" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="58" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D58">
         <v>57</v>
       </c>
@@ -11748,7 +11749,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="59" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="59" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D59">
         <v>58</v>
       </c>
@@ -11771,7 +11772,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="60" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="60" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D60">
         <v>59</v>
       </c>
@@ -11794,7 +11795,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="61" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="61" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D61">
         <v>60</v>
       </c>
@@ -11817,7 +11818,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="62" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="62" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D62">
         <v>61</v>
       </c>
@@ -11840,7 +11841,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="63" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="63" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D63">
         <v>62</v>
       </c>
@@ -11863,7 +11864,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="64" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="64" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D64">
         <v>63</v>
       </c>
@@ -11886,7 +11887,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="65" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="65" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D65">
         <v>64</v>
       </c>
@@ -11909,7 +11910,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="66" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="66" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D66">
         <v>65</v>
       </c>
@@ -11932,7 +11933,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="67" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="67" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D67">
         <v>66</v>
       </c>
@@ -11955,7 +11956,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="68" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="68" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D68">
         <v>67</v>
       </c>
@@ -11978,7 +11979,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="69" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="69" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D69">
         <v>68</v>
       </c>
@@ -12001,7 +12002,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="70" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="70" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D70">
         <v>69</v>
       </c>
@@ -12024,7 +12025,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="71" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="71" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D71">
         <v>70</v>
       </c>
@@ -12047,7 +12048,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="72" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="72" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D72">
         <v>71</v>
       </c>
@@ -12070,7 +12071,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="73" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="73" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D73">
         <v>72</v>
       </c>
@@ -12093,7 +12094,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="74" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="74" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D74">
         <v>73</v>
       </c>
@@ -12116,7 +12117,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="75" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="75" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D75">
         <v>74</v>
       </c>
@@ -12139,7 +12140,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="76" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="76" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D76">
         <v>75</v>
       </c>
@@ -12162,7 +12163,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="77" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="77" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D77">
         <v>76</v>
       </c>
@@ -12185,7 +12186,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="78" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="78" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D78">
         <v>77</v>
       </c>
@@ -12208,7 +12209,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="79" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="79" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D79">
         <v>78</v>
       </c>
@@ -12231,7 +12232,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="80" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="80" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D80">
         <v>79</v>
       </c>
@@ -12254,7 +12255,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="81" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="81" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D81">
         <v>80</v>
       </c>
@@ -12277,7 +12278,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="82" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="82" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D82">
         <v>81</v>
       </c>
@@ -12300,7 +12301,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="83" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="83" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D83">
         <v>82</v>
       </c>
@@ -12323,7 +12324,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="84" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="84" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D84">
         <v>83</v>
       </c>
@@ -12346,7 +12347,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="85" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="85" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D85">
         <v>84</v>
       </c>
@@ -12369,7 +12370,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="86" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="86" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D86">
         <v>85</v>
       </c>
@@ -12392,7 +12393,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="87" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="87" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D87">
         <v>86</v>
       </c>
@@ -12415,7 +12416,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="88" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="88" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D88">
         <v>87</v>
       </c>
@@ -12438,7 +12439,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="89" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="89" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D89">
         <v>88</v>
       </c>
@@ -12461,7 +12462,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="90" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="90" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D90">
         <v>89</v>
       </c>
@@ -12484,7 +12485,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="91" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="91" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D91">
         <v>90</v>
       </c>
@@ -12507,7 +12508,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="92" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="92" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D92">
         <v>91</v>
       </c>
@@ -12530,7 +12531,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="93" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="93" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D93">
         <v>92</v>
       </c>
@@ -12553,7 +12554,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="94" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="94" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D94">
         <v>93</v>
       </c>
@@ -12576,7 +12577,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="95" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="95" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D95">
         <v>94</v>
       </c>
@@ -12599,7 +12600,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="96" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="96" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D96">
         <v>95</v>
       </c>
@@ -12622,7 +12623,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="97" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="97" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D97">
         <v>96</v>
       </c>
@@ -12645,7 +12646,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="98" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="98" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D98">
         <v>97</v>
       </c>
@@ -12668,7 +12669,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="99" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="99" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D99">
         <v>98</v>
       </c>
@@ -12691,7 +12692,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="100" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="100" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D100">
         <v>99</v>
       </c>
@@ -12714,7 +12715,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="101" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="101" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D101">
         <v>100</v>
       </c>
@@ -12737,7 +12738,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="102" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="102" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D102">
         <v>101</v>
       </c>
@@ -12760,7 +12761,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="103" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="103" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D103">
         <v>102</v>
       </c>
@@ -12783,7 +12784,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="104" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="104" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D104">
         <v>103</v>
       </c>
@@ -12806,7 +12807,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="105" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="105" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D105">
         <v>104</v>
       </c>
@@ -12829,7 +12830,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="106" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="106" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D106">
         <v>105</v>
       </c>
@@ -12852,7 +12853,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="107" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="107" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D107">
         <v>106</v>
       </c>
@@ -12875,7 +12876,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="108" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="108" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D108">
         <v>107</v>
       </c>
@@ -12898,7 +12899,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="109" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="109" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D109">
         <v>108</v>
       </c>
@@ -12921,7 +12922,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="110" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="110" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D110">
         <v>109</v>
       </c>
@@ -12944,7 +12945,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="111" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="111" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D111">
         <v>110</v>
       </c>
@@ -12967,7 +12968,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="112" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="112" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D112">
         <v>111</v>
       </c>
@@ -12990,7 +12991,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="113" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="113" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D113">
         <v>112</v>
       </c>
@@ -13013,7 +13014,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="114" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="114" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D114">
         <v>113</v>
       </c>
@@ -13036,7 +13037,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="115" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="115" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D115">
         <v>114</v>
       </c>
@@ -13059,7 +13060,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="116" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="116" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D116">
         <v>115</v>
       </c>
@@ -13082,7 +13083,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="117" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="117" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D117">
         <v>116</v>
       </c>
@@ -13105,7 +13106,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="118" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="118" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D118">
         <v>117</v>
       </c>
@@ -13128,7 +13129,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="119" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="119" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D119">
         <v>118</v>
       </c>
@@ -13151,7 +13152,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="120" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="120" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D120">
         <v>119</v>
       </c>
@@ -13174,7 +13175,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="121" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="121" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D121">
         <v>120</v>
       </c>
@@ -13197,7 +13198,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="122" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="122" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D122">
         <v>121</v>
       </c>
@@ -13220,7 +13221,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="123" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="123" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D123">
         <v>122</v>
       </c>
@@ -13243,7 +13244,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="124" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="124" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D124">
         <v>123</v>
       </c>
@@ -13266,7 +13267,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="125" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="125" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D125">
         <v>124</v>
       </c>
@@ -13289,7 +13290,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="126" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="126" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D126">
         <v>125</v>
       </c>
@@ -13312,7 +13313,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="127" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="127" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D127">
         <v>126</v>
       </c>
@@ -13335,7 +13336,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="128" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="128" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D128">
         <v>127</v>
       </c>
@@ -13358,7 +13359,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="129" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="129" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D129">
         <v>128</v>
       </c>
@@ -13381,7 +13382,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="130" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="130" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D130">
         <v>129</v>
       </c>
@@ -13404,7 +13405,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="131" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="131" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D131">
         <v>130</v>
       </c>
@@ -13427,7 +13428,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="132" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="132" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D132">
         <v>131</v>
       </c>
@@ -13450,7 +13451,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="133" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="133" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D133">
         <v>132</v>
       </c>
@@ -13473,7 +13474,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="134" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="134" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D134">
         <v>133</v>
       </c>
@@ -13496,7 +13497,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="135" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="135" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D135">
         <v>134</v>
       </c>
@@ -13519,7 +13520,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="136" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="136" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D136">
         <v>135</v>
       </c>
@@ -13542,7 +13543,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="137" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="137" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D137">
         <v>136</v>
       </c>
@@ -13565,7 +13566,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="138" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="138" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D138">
         <v>137</v>
       </c>
@@ -13588,7 +13589,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="139" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="139" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D139">
         <v>138</v>
       </c>
@@ -13611,7 +13612,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="140" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="140" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D140">
         <v>139</v>
       </c>
@@ -13634,7 +13635,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="141" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="141" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D141">
         <v>140</v>
       </c>
@@ -13657,7 +13658,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="142" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="142" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D142">
         <v>141</v>
       </c>
@@ -13680,7 +13681,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="143" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="143" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D143">
         <v>142</v>
       </c>
@@ -13703,7 +13704,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="144" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="144" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D144">
         <v>143</v>
       </c>
@@ -13726,7 +13727,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="145" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="145" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D145">
         <v>144</v>
       </c>
@@ -13749,7 +13750,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="146" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="146" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D146">
         <v>145</v>
       </c>
@@ -13772,7 +13773,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="147" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="147" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D147">
         <v>146</v>
       </c>
@@ -13795,7 +13796,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="148" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="148" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D148">
         <v>147</v>
       </c>
@@ -13818,7 +13819,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="149" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="149" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D149">
         <v>148</v>
       </c>
@@ -13841,7 +13842,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="150" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="150" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D150">
         <v>149</v>
       </c>
@@ -13864,7 +13865,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="151" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="151" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D151">
         <v>150</v>
       </c>
@@ -13887,7 +13888,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="152" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="152" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D152">
         <v>151</v>
       </c>
@@ -13910,7 +13911,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="153" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="153" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D153">
         <v>152</v>
       </c>
@@ -13933,7 +13934,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="154" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="154" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D154">
         <v>153</v>
       </c>
@@ -13956,7 +13957,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="155" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="155" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D155">
         <v>154</v>
       </c>
@@ -13979,7 +13980,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="156" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="156" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D156">
         <v>155</v>
       </c>
@@ -14002,7 +14003,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="157" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="157" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D157">
         <v>156</v>
       </c>
@@ -14025,7 +14026,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="158" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="158" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D158">
         <v>157</v>
       </c>
@@ -14048,7 +14049,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="159" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="159" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D159">
         <v>158</v>
       </c>
@@ -14071,7 +14072,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="160" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="160" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D160">
         <v>159</v>
       </c>
@@ -14094,7 +14095,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="161" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="161" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D161">
         <v>160</v>
       </c>
@@ -14117,7 +14118,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="162" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="162" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D162">
         <v>161</v>
       </c>
@@ -14140,7 +14141,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="163" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="163" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D163">
         <v>162</v>
       </c>
@@ -14163,7 +14164,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="164" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="164" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D164">
         <v>163</v>
       </c>
@@ -14186,7 +14187,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="165" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="165" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D165">
         <v>164</v>
       </c>
@@ -14209,7 +14210,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="166" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="166" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D166">
         <v>165</v>
       </c>
@@ -14232,7 +14233,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="167" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="167" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D167">
         <v>166</v>
       </c>
@@ -14255,7 +14256,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="168" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="168" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D168">
         <v>167</v>
       </c>
@@ -14278,7 +14279,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="169" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="169" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D169">
         <v>168</v>
       </c>
@@ -14301,7 +14302,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="170" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="170" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D170">
         <v>169</v>
       </c>
@@ -14324,7 +14325,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="171" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="171" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D171">
         <v>170</v>
       </c>
@@ -14347,7 +14348,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="172" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="172" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D172">
         <v>171</v>
       </c>
@@ -14370,7 +14371,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="173" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="173" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D173">
         <v>172</v>
       </c>
@@ -14393,7 +14394,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="174" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="174" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D174">
         <v>173</v>
       </c>
@@ -14416,7 +14417,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="175" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="175" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D175">
         <v>174</v>
       </c>
@@ -14439,7 +14440,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="176" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="176" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D176">
         <v>175</v>
       </c>
@@ -14462,7 +14463,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="177" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="177" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D177">
         <v>176</v>
       </c>
@@ -14485,7 +14486,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="178" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="178" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D178">
         <v>177</v>
       </c>
@@ -14508,7 +14509,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="179" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="179" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D179">
         <v>178</v>
       </c>
@@ -14531,7 +14532,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="180" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="180" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D180">
         <v>179</v>
       </c>
@@ -14554,7 +14555,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="181" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="181" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D181">
         <v>180</v>
       </c>
@@ -14577,7 +14578,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="182" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="182" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D182">
         <v>181</v>
       </c>
@@ -14600,7 +14601,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="183" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="183" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D183">
         <v>182</v>
       </c>
@@ -14623,7 +14624,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="184" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="184" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D184">
         <v>183</v>
       </c>
@@ -14646,7 +14647,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="185" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="185" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D185">
         <v>184</v>
       </c>
@@ -14669,7 +14670,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="186" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="186" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D186">
         <v>185</v>
       </c>
@@ -14692,7 +14693,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="187" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="187" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D187">
         <v>186</v>
       </c>
@@ -14715,7 +14716,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="188" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="188" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D188">
         <v>187</v>
       </c>
@@ -14738,7 +14739,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="189" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="189" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D189">
         <v>188</v>
       </c>
@@ -14761,7 +14762,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="190" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="190" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D190">
         <v>189</v>
       </c>
@@ -14784,7 +14785,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="191" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="191" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D191">
         <v>190</v>
       </c>
@@ -14807,7 +14808,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="192" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="192" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D192">
         <v>191</v>
       </c>
@@ -14830,7 +14831,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="193" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="193" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D193">
         <v>192</v>
       </c>
@@ -14853,7 +14854,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="194" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="194" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A194">
         <v>381</v>
       </c>
@@ -14876,7 +14877,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="195" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="195" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A195">
         <v>382</v>
       </c>
@@ -14899,7 +14900,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="196" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="196" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A196">
         <v>383</v>
       </c>
@@ -14922,7 +14923,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="197" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="197" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A197">
         <v>384</v>
       </c>
@@ -14945,7 +14946,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="198" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="198" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A198">
         <v>385</v>
       </c>
@@ -14968,7 +14969,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="199" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="199" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A199">
         <v>386</v>
       </c>
@@ -14991,7 +14992,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="200" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="200" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A200">
         <v>387</v>
       </c>
@@ -15014,7 +15015,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="201" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="201" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A201">
         <v>388</v>
       </c>
